--- a/Grupinis/KainuStebejimas.xlsx
+++ b/Grupinis/KainuStebejimas.xlsx
@@ -5,20 +5,24 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vejas\OneDrive\Documents\UiPath\Grupinis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vejas\OneDrive\Documents\UiPath\RPA\Grupinis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4369862D-CD84-4E07-A96E-612CEDD860DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A3CDA3-A493-462C-99A4-F667730FAD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parduotuvės" sheetId="2" r:id="rId1"/>
     <sheet name="Prekės" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
     <sheet name="Kainos" sheetId="1" r:id="rId4"/>
+    <sheet name="Kainų suvestinė" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <pivotCaches>
+    <pivotCache cacheId="19" r:id="rId6"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="32">
   <si>
     <t>Parduotuvė</t>
   </si>
@@ -96,31 +100,34 @@
     <t>Nėra</t>
   </si>
   <si>
-    <t>3,90</t>
-  </si>
-  <si>
     <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-editions-football-fifa-world-cup-oficiali?id=254734272</t>
   </si>
   <si>
-    <t>189,99</t>
-  </si>
-  <si>
-    <t>155,85</t>
-  </si>
-  <si>
     <t>https://www.lego.com/en-lt/product/fifa-world-cup-official-trophy-43020</t>
   </si>
   <si>
-    <t>6,00</t>
-  </si>
-  <si>
-    <t>145,39</t>
-  </si>
-  <si>
     <t>Liko tik: 4 vnt.</t>
   </si>
   <si>
     <t>Yra</t>
+  </si>
+  <si>
+    <t>Galutinė kaina</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Min of Galutinė kaina</t>
   </si>
 </sst>
 </file>
@@ -173,7 +180,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -190,6 +197,11 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -206,6 +218,322 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46164.786146527775" createdVersion="1" refreshedVersion="8" recordCount="12" xr:uid="{29909672-C663-491E-A5D5-82DFC9BA2D10}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:I13" sheet="Kainos"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="Parduotuvė" numFmtId="0">
+      <sharedItems containsBlank="1" count="4">
+        <s v="varle.lt"/>
+        <s v="pigu.lt"/>
+        <s v="lego.com"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Prekė" numFmtId="0">
+      <sharedItems containsBlank="1" count="2">
+        <s v="LEGO 43020"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Nuoroda" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Įprasta kaina" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="145.38999999999999" maxValue="189.99"/>
+    </cacheField>
+    <cacheField name="Kaina su nuolaida" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="155.85" maxValue="155.85"/>
+    </cacheField>
+    <cacheField name="Siuntimo kaina" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="3.49" maxValue="6"/>
+    </cacheField>
+    <cacheField name="Ar prekė yra?" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Tikrinimo laikas" numFmtId="22">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-05-22T18:51:39" maxDate="2026-05-22T18:51:59"/>
+    </cacheField>
+    <cacheField name="Galutinė kaina" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="149.29" maxValue="195.99"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="https://www.varle.lt/lego/lego-editions-fifa-world-cuptm-oficiali-taure--50253636.html"/>
+    <n v="145.38999999999999"/>
+    <s v="Nėra"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 4 vnt."/>
+    <d v="2026-05-22T18:51:39"/>
+    <n v="149.29"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-editions-football-fifa-world-cup-oficiali?id=254734272"/>
+    <n v="189.99"/>
+    <n v="155.85"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-22T18:51:48"/>
+    <n v="159.34"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="https://www.lego.com/en-lt/product/fifa-world-cup-official-trophy-43020"/>
+    <n v="189.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Yra"/>
+    <d v="2026-05-22T18:51:59"/>
+    <n v="195.99"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2FBB168E-AC67-477E-85E9-C2B74541AC70}" name="Kainų palyginimas" cacheId="19" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
+  <location ref="A1:F5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField axis="axisCol" showAll="0" includeNewItemsInFilter="1">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField dataField="1" showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Min of Galutinė kaina" fld="8" subtotal="min" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -587,7 +915,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -602,7 +930,7 @@
     <col min="10" max="10" width="19.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -627,8 +955,11 @@
       <c r="H1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -638,23 +969,26 @@
       <c r="C2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>28</v>
+      <c r="D2" s="6">
+        <v>145.38999999999999</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>22</v>
+      <c r="F2" s="4">
+        <v>3.9</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H2" s="2">
-        <v>46164.684861111113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>46164.785868055558</v>
+      </c>
+      <c r="I2">
+        <v>149.29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -662,25 +996,28 @@
         <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="D3" s="7">
+        <v>189.99</v>
+      </c>
+      <c r="E3" s="5">
+        <v>155.85</v>
       </c>
       <c r="F3" s="4">
         <v>3.49</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H3" s="2">
-        <v>46164.684942129628</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>46164.78597222222</v>
+      </c>
+      <c r="I3">
+        <v>159.34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -688,32 +1025,35 @@
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="D4" s="7">
+        <v>189.99</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>27</v>
+      <c r="F4" s="4">
+        <v>6</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H4" s="2">
-        <v>46164.685034722221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>46164.786099537036</v>
+      </c>
+      <c r="I4">
+        <v>195.99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="4"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C6" s="3"/>
       <c r="D6" s="5"/>
       <c r="E6" s="4"/>
@@ -721,43 +1061,43 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D8" s="7"/>
       <c r="E8" s="5"/>
       <c r="F8" s="4"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D9" s="6"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D10" s="6"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D11" s="6"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D13" s="6"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -771,4 +1111,94 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C1CC2D0-D9C9-4997-BBAE-0EEAAC63CBD1}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="10">
+        <v>195.99</v>
+      </c>
+      <c r="C3" s="10">
+        <v>159.34</v>
+      </c>
+      <c r="D3" s="10">
+        <v>149.29</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10">
+        <v>149.29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="10">
+        <v>195.99</v>
+      </c>
+      <c r="C5" s="10">
+        <v>159.34</v>
+      </c>
+      <c r="D5" s="10">
+        <v>149.29</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10">
+        <v>149.29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Grupinis/KainuStebejimas.xlsx
+++ b/Grupinis/KainuStebejimas.xlsx
@@ -1,38 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vejas\OneDrive\Documents\UiPath\RPA\Grupinis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A3CDA3-A493-462C-99A4-F667730FAD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4579772-635D-45BB-9784-D6C9B9D95AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parduotuvės" sheetId="2" r:id="rId1"/>
     <sheet name="Prekės" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
-    <sheet name="Kainos" sheetId="1" r:id="rId4"/>
-    <sheet name="Kainų suvestinė" sheetId="5" r:id="rId5"/>
+    <sheet name="Kainos" sheetId="5" r:id="rId3"/>
+    <sheet name="Pigiausia" sheetId="6" r:id="rId4"/>
+    <sheet name="Kainų suvestinė" sheetId="7" r:id="rId5"/>
+    <sheet name="Pardavėjų vertinimas" sheetId="8" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="19" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="70">
   <si>
     <t>Parduotuvė</t>
   </si>
@@ -67,9 +81,21 @@
     <t>Prekė</t>
   </si>
   <si>
+    <t>varle.lt</t>
+  </si>
+  <si>
+    <t>pigu.lt</t>
+  </si>
+  <si>
+    <t>lego.com</t>
+  </si>
+  <si>
     <t>Nuoroda</t>
   </si>
   <si>
+    <t>Įprasta kaina</t>
+  </si>
+  <si>
     <t>Kaina su nuolaida</t>
   </si>
   <si>
@@ -82,22 +108,40 @@
     <t>Tikrinimo laikas</t>
   </si>
   <si>
-    <t>Įprasta kaina</t>
-  </si>
-  <si>
-    <t>varle.lt</t>
-  </si>
-  <si>
-    <t>pigu.lt</t>
-  </si>
-  <si>
-    <t>lego.com</t>
+    <t>Galutinė kaina</t>
+  </si>
+  <si>
+    <t>Nėra</t>
+  </si>
+  <si>
+    <t>Yra</t>
+  </si>
+  <si>
+    <t>https://www.varle.lt/lego/lego-botanicals-zydintis-kaktusas-augalu-dekoras--50745550.html</t>
+  </si>
+  <si>
+    <t>Liko tik: 5+ vnt.</t>
+  </si>
+  <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-zydintis-kaktusas-11509?id=249971577</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/en-lt/product/flowering-cactus-11509</t>
+  </si>
+  <si>
+    <t>https://www.varle.lt/lego/lego-besisupantys-augalai--53770717.html</t>
+  </si>
+  <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-besisupantys-augalai-geliu-rinkinys-11506?id=256483817</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/en-lt/product/rocking-plants-11506</t>
   </si>
   <si>
     <t>https://www.varle.lt/lego/lego-editions-fifa-world-cuptm-oficiali-taure--50253636.html</t>
   </si>
   <si>
-    <t>Nėra</t>
+    <t>Liko tik: 3 vnt.</t>
   </si>
   <si>
     <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-editions-football-fifa-world-cup-oficiali?id=254734272</t>
@@ -106,28 +150,112 @@
     <t>https://www.lego.com/en-lt/product/fifa-world-cup-official-trophy-43020</t>
   </si>
   <si>
-    <t>Liko tik: 4 vnt.</t>
-  </si>
-  <si>
-    <t>Yra</t>
-  </si>
-  <si>
-    <t>Galutinė kaina</t>
+    <t>https://www.varle.lt/robotai-ismanus-zaislai/lego-minecraft-lis-21588--53525886.html</t>
+  </si>
+  <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-minecraft-lape-21588?id=249971612</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/en-lt/product/the-fox-21588</t>
+  </si>
+  <si>
+    <t>https://www.varle.lt/lego/lego-art-love-31214--41770074.html</t>
+  </si>
+  <si>
+    <t>Liko tik: 2 vnt.</t>
+  </si>
+  <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-art-love-31214?id=116946294</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/en-lt/product/love-31214</t>
+  </si>
+  <si>
+    <t>https://www.varle.lt/lego/lego-icons-bonsai-medelis-10281--15106778.html</t>
+  </si>
+  <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-bonsai-medelis-10281?id=36407853</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/en-lt/product/bonsai-tree-10281</t>
+  </si>
+  <si>
+    <t>https://www.varle.lt/lego/lego-harry-potter-hagrido-ir-hario-pasivazinejimas--41842791.html</t>
+  </si>
+  <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/76443-lego-harry-potter-hagrido-ir-hario?id=125603664</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/en-lt/product/hagrid-harrys-motorcycle-ride-76443</t>
+  </si>
+  <si>
+    <t>https://www.varle.lt/lego/lego-icons-mclaren-mp44-ir-ayrton-senna-10330--32593893.html</t>
+  </si>
+  <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-icons-mclaren-mp44-ir-ayrton-senna?id=80634865</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/en-lt/product/mclaren-mp44-ayrton-senna-10330</t>
+  </si>
+  <si>
+    <t>Pigu.lt</t>
+  </si>
+  <si>
+    <t>Varle.lt</t>
+  </si>
+  <si>
+    <t>Lego.com</t>
+  </si>
+  <si>
+    <t>Pigiausia</t>
+  </si>
+  <si>
+    <t>varle.lt - 25.689999999999998</t>
+  </si>
+  <si>
+    <t>varle.lt - 18.66</t>
+  </si>
+  <si>
+    <t>pigu.lt - 159.34</t>
+  </si>
+  <si>
+    <t>lego.com - 52.99</t>
+  </si>
+  <si>
+    <t>varle.lt - 66.46000000000001</t>
+  </si>
+  <si>
+    <t>varle.lt - 44.89</t>
+  </si>
+  <si>
+    <t>pigu.lt - 45.39</t>
+  </si>
+  <si>
+    <t>varle.lt - 71.89</t>
   </si>
   <si>
     <t>Row Labels</t>
   </si>
   <si>
-    <t>(blank)</t>
-  </si>
-  <si>
     <t>Grand Total</t>
   </si>
   <si>
-    <t>Column Labels</t>
-  </si>
-  <si>
-    <t>Min of Galutinė kaina</t>
+    <t>Average of Pigu.lt</t>
+  </si>
+  <si>
+    <t>Average of Varle.lt</t>
+  </si>
+  <si>
+    <t>Average of Lego.com</t>
+  </si>
+  <si>
+    <t>Sum of Galutinė kaina</t>
+  </si>
+  <si>
+    <t>varle.lt - 25.69</t>
+  </si>
+  <si>
+    <t>aaaaaaaaasfdasdasdasdasomdasldpmasdopamsd</t>
   </si>
 </sst>
 </file>
@@ -180,28 +308,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -221,45 +339,80 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46164.786146527775" createdVersion="1" refreshedVersion="8" recordCount="12" xr:uid="{29909672-C663-491E-A5D5-82DFC9BA2D10}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46165.745033680556" createdVersion="1" refreshedVersion="8" recordCount="10" xr:uid="{8ACD45B7-58CD-4D19-B6F1-AB000FB66EE0}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:I13" sheet="Kainos"/>
+    <worksheetSource ref="A1:E11" sheet="Pigiausia"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Prekė" numFmtId="0">
+      <sharedItems count="8">
+        <s v="LEGO 11509"/>
+        <s v="LEGO 11506"/>
+        <s v="LEGO 43020"/>
+        <s v="LEGO 21588"/>
+        <s v="LEGO 31214"/>
+        <s v="LEGO 10281"/>
+        <s v="LEGO 76443"/>
+        <s v="LEGO 10330"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Pigu.lt" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="24.619999999999902" maxValue="159.34"/>
+    </cacheField>
+    <cacheField name="Varle.lt" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="18.66" maxValue="159.89000000000001"/>
+    </cacheField>
+    <cacheField name="Lego.com" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="25.99" maxValue="195.99"/>
+    </cacheField>
+    <cacheField name="Pigiausia" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46165.745051967591" createdVersion="1" refreshedVersion="8" recordCount="30" xr:uid="{35F765EF-BAEA-45AC-929D-E2C85667C430}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:I31" sheet="Kainos"/>
   </cacheSource>
   <cacheFields count="9">
     <cacheField name="Parduotuvė" numFmtId="0">
-      <sharedItems containsBlank="1" count="4">
+      <sharedItems count="3">
         <s v="varle.lt"/>
         <s v="pigu.lt"/>
         <s v="lego.com"/>
-        <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="Prekė" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="LEGO 43020"/>
-        <m/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Nuoroda" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+      <sharedItems/>
     </cacheField>
-    <cacheField name="Įprasta kaina" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="145.38999999999999" maxValue="189.99"/>
+    <cacheField name="Įprasta kaina" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="14.76" maxValue="189.99"/>
     </cacheField>
-    <cacheField name="Kaina su nuolaida" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="155.85" maxValue="155.85"/>
+    <cacheField name="Kaina su nuolaida" numFmtId="2">
+      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="30.34" maxValue="155.85"/>
     </cacheField>
-    <cacheField name="Siuntimo kaina" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="3.49" maxValue="6"/>
+    <cacheField name="Siuntimo kaina" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.49" maxValue="6"/>
     </cacheField>
     <cacheField name="Ar prekė yra?" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Tikrinimo laikas" numFmtId="22">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-05-22T18:51:39" maxDate="2026-05-22T18:51:59"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-23T17:32:38" maxDate="2026-05-23T17:52:49"/>
     </cacheField>
     <cacheField name="Galutinė kaina" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="149.29" maxValue="195.99"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="18.66" maxValue="195.99"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -271,152 +424,429 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="10">
   <r>
     <x v="0"/>
+    <n v="33.83"/>
+    <n v="25.69"/>
+    <n v="37.989999999999995"/>
+    <s v="varle.lt - 25.69"/>
+  </r>
+  <r>
     <x v="0"/>
-    <s v="https://www.varle.lt/lego/lego-editions-fifa-world-cuptm-oficiali-taure--50253636.html"/>
-    <n v="145.38999999999999"/>
+    <n v="33.83"/>
+    <n v="25.689999999999998"/>
+    <n v="37.989999999999995"/>
+    <s v="varle.lt - 25.689999999999998"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="24.619999999999902"/>
+    <n v="18.66"/>
+    <n v="25.99"/>
+    <s v="varle.lt - 18.66"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="159.34"/>
+    <n v="159.89000000000001"/>
+    <n v="195.99"/>
+    <s v="pigu.lt - 159.34"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="53.44"/>
+    <n v="55.47"/>
+    <n v="52.99"/>
+    <s v="lego.com - 52.99"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="79.05"/>
+    <n v="66.460000000000008"/>
+    <n v="93.99"/>
+    <s v="varle.lt - 66.46000000000001"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="159.34"/>
+    <n v="159.89000000000001"/>
+    <n v="195.99"/>
+    <s v="pigu.lt - 159.34"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="57.64"/>
+    <n v="44.89"/>
+    <n v="65.990000000000009"/>
+    <s v="varle.lt - 44.89"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="45.39"/>
+    <n v="45.89"/>
+    <n v="60.99"/>
+    <s v="pigu.lt - 45.39"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="73.489999999999995"/>
+    <n v="71.89"/>
+    <n v="100.99"/>
+    <s v="varle.lt - 71.89"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="30">
+  <r>
+    <x v="0"/>
+    <s v="LEGO 11509"/>
+    <s v="https://www.varle.lt/lego/lego-botanicals-zydintis-kaktusas-augalu-dekoras--50745550.html"/>
+    <n v="21.79"/>
     <s v="Nėra"/>
     <n v="3.9"/>
-    <s v="Liko tik: 4 vnt."/>
-    <d v="2026-05-22T18:51:39"/>
-    <n v="149.29"/>
+    <s v="Liko tik: 5+ vnt."/>
+    <d v="2026-05-23T17:52:35"/>
+    <n v="25.689999999999998"/>
   </r>
   <r>
     <x v="1"/>
+    <s v="LEGO 11509"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-zydintis-kaktusas-11509?id=249971577"/>
+    <n v="31.99"/>
+    <n v="30.34"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:52:42"/>
+    <n v="33.83"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="LEGO 11509"/>
+    <s v="https://www.lego.com/en-lt/product/flowering-cactus-11509"/>
+    <n v="31.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:52:49"/>
+    <n v="37.989999999999995"/>
+  </r>
+  <r>
     <x v="0"/>
+    <s v="LEGO 11509"/>
+    <s v="https://www.varle.lt/lego/lego-botanicals-zydintis-kaktusas-augalu-dekoras--50745550.html"/>
+    <n v="21.79"/>
+    <s v="Nėra"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 5+ vnt."/>
+    <d v="2026-05-23T17:32:38"/>
+    <n v="25.689999999999998"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="LEGO 11509"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-zydintis-kaktusas-11509?id=249971577"/>
+    <n v="31.99"/>
+    <n v="30.34"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:32:44"/>
+    <n v="33.83"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="LEGO 11509"/>
+    <s v="https://www.lego.com/en-lt/product/flowering-cactus-11509"/>
+    <n v="31.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:32:50"/>
+    <n v="37.989999999999995"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="LEGO 11506"/>
+    <s v="https://www.varle.lt/lego/lego-besisupantys-augalai--53770717.html"/>
+    <n v="14.76"/>
+    <s v="Nėra"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 5+ vnt."/>
+    <d v="2026-05-23T17:32:58"/>
+    <n v="18.66"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="LEGO 11506"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-besisupantys-augalai-geliu-rinkinys-11506?id=256483817"/>
+    <n v="21.13"/>
+    <s v="Nėra"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:33:05"/>
+    <n v="24.619999999999997"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="LEGO 11506"/>
+    <s v="https://www.lego.com/en-lt/product/rocking-plants-11506"/>
+    <n v="19.989999999999998"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:33:12"/>
+    <n v="25.99"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="LEGO 43020"/>
+    <s v="https://www.varle.lt/lego/lego-editions-fifa-world-cuptm-oficiali-taure--50253636.html"/>
+    <n v="155.99"/>
+    <s v="Nėra"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 3 vnt."/>
+    <d v="2026-05-23T17:33:20"/>
+    <n v="159.89000000000001"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="LEGO 43020"/>
     <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-editions-football-fifa-world-cup-oficiali?id=254734272"/>
     <n v="189.99"/>
     <n v="155.85"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-22T18:51:48"/>
+    <d v="2026-05-23T17:33:26"/>
     <n v="159.34"/>
   </r>
   <r>
     <x v="2"/>
-    <x v="0"/>
+    <s v="LEGO 43020"/>
     <s v="https://www.lego.com/en-lt/product/fifa-world-cup-official-trophy-43020"/>
     <n v="189.99"/>
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Yra"/>
-    <d v="2026-05-22T18:51:59"/>
+    <d v="2026-05-23T17:33:33"/>
     <n v="195.99"/>
   </r>
   <r>
-    <x v="3"/>
+    <x v="0"/>
+    <s v="LEGO 21588"/>
+    <s v="https://www.varle.lt/robotai-ismanus-zaislai/lego-minecraft-lis-21588--53525886.html"/>
+    <n v="52.97"/>
+    <n v="51.57"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 5+ vnt."/>
+    <d v="2026-05-23T17:33:40"/>
+    <n v="55.47"/>
+  </r>
+  <r>
     <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="3"/>
+    <s v="LEGO 21588"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-minecraft-lape-21588?id=249971612"/>
+    <n v="49.95"/>
+    <s v="Nėra"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:33:47"/>
+    <n v="53.440000000000005"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="LEGO 21588"/>
+    <s v="https://www.lego.com/en-lt/product/the-fox-21588"/>
+    <n v="46.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:33:53"/>
+    <n v="52.99"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="LEGO 31214"/>
+    <s v="https://www.varle.lt/lego/lego-art-love-31214--41770074.html"/>
+    <n v="72.989999999999995"/>
+    <n v="62.56"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 2 vnt."/>
+    <d v="2026-05-23T17:34:00"/>
+    <n v="66.460000000000008"/>
+  </r>
+  <r>
     <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="3"/>
+    <s v="LEGO 31214"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-art-love-31214?id=116946294"/>
+    <n v="87.99"/>
+    <n v="75.56"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:34:07"/>
+    <n v="79.05"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="LEGO 31214"/>
+    <s v="https://www.lego.com/en-lt/product/love-31214"/>
+    <n v="87.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:34:13"/>
+    <n v="93.99"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="LEGO 43020"/>
+    <s v="https://www.varle.lt/lego/lego-editions-fifa-world-cuptm-oficiali-taure--50253636.html"/>
+    <n v="155.99"/>
+    <s v="Nėra"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 3 vnt."/>
+    <d v="2026-05-23T17:34:23"/>
+    <n v="159.89000000000001"/>
+  </r>
+  <r>
     <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="3"/>
+    <s v="LEGO 43020"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-editions-football-fifa-world-cup-oficiali?id=254734272"/>
+    <n v="189.99"/>
+    <n v="155.85"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:34:29"/>
+    <n v="159.34"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="LEGO 43020"/>
+    <s v="https://www.lego.com/en-lt/product/fifa-world-cup-official-trophy-43020"/>
+    <n v="189.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:34:36"/>
+    <n v="195.99"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="LEGO 10281"/>
+    <s v="https://www.varle.lt/lego/lego-icons-bonsai-medelis-10281--15106778.html"/>
+    <n v="48.99"/>
+    <n v="40.99"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 5+ vnt."/>
+    <d v="2026-05-23T17:34:43"/>
+    <n v="44.89"/>
+  </r>
+  <r>
     <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="3"/>
+    <s v="LEGO 10281"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-bonsai-medelis-10281?id=36407853"/>
+    <n v="54.15"/>
+    <s v="Nėra"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:34:51"/>
+    <n v="57.64"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="LEGO 10281"/>
+    <s v="https://www.lego.com/en-lt/product/bonsai-tree-10281"/>
+    <n v="59.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:34:57"/>
+    <n v="65.990000000000009"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="LEGO 76443"/>
+    <s v="https://www.varle.lt/lego/lego-harry-potter-hagrido-ir-hario-pasivazinejimas--41842791.html"/>
+    <n v="42.99"/>
+    <n v="41.99"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 5+ vnt."/>
+    <d v="2026-05-23T17:35:04"/>
+    <n v="45.89"/>
+  </r>
+  <r>
     <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="3"/>
+    <s v="LEGO 76443"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/76443-lego-harry-potter-hagrido-ir-hario?id=125603664"/>
+    <n v="54.99"/>
+    <n v="41.9"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:35:11"/>
+    <n v="45.39"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="LEGO 76443"/>
+    <s v="https://www.lego.com/en-lt/product/hagrid-harrys-motorcycle-ride-76443"/>
+    <n v="54.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:35:17"/>
+    <n v="60.99"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="LEGO 10330"/>
+    <s v="https://www.varle.lt/lego/lego-icons-mclaren-mp44-ir-ayrton-senna-10330--32593893.html"/>
+    <n v="72.989999999999995"/>
+    <n v="67.989999999999995"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 5+ vnt."/>
+    <d v="2026-05-23T17:35:24"/>
+    <n v="71.89"/>
+  </r>
+  <r>
     <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="LEGO 10330"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-icons-mclaren-mp44-ir-ayrton-senna?id=80634865"/>
+    <n v="94.99"/>
+    <n v="70"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:35:30"/>
+    <n v="73.489999999999995"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="LEGO 10330"/>
+    <s v="https://www.lego.com/en-lt/product/mclaren-mp44-ayrton-senna-10330"/>
+    <n v="94.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T17:35:37"/>
+    <n v="100.99"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2FBB168E-AC67-477E-85E9-C2B74541AC70}" name="Kainų palyginimas" cacheId="19" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
-  <location ref="A1:F5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField axis="axisCol" showAll="0" includeNewItemsInFilter="1">
-      <items count="5">
-        <item x="2"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BC89E6C5-8E2C-4B47-BFC3-3A55CB5A3665}" name="Vidutinė kaina" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
+  <location ref="A1:D10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
+      <items count="9">
+        <item x="5"/>
+        <item x="7"/>
         <item x="1"/>
         <item x="0"/>
         <item x="3"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="6"/>
         <item t="default"/>
       </items>
       <extLst>
@@ -425,10 +855,107 @@
         </ext>
       </extLst>
     </pivotField>
+    <pivotField dataField="1" showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField dataField="1" showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField dataField="1" showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Average of Pigu.lt" fld="1" subtotal="average" baseField="0" baseItem="0"/>
+    <dataField name="Average of Varle.lt" fld="2" subtotal="average" baseField="0" baseItem="0"/>
+    <dataField name="Average of Lego.com" fld="3" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C8789DDD-3966-48A0-93FD-759D3D65D707}" name="Parduotuvių vertinimas" cacheId="1" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
+  <location ref="A1:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
-      <items count="3">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
         <item x="0"/>
-        <item x="1"/>
         <item t="default"/>
       </items>
       <extLst>
@@ -451,7 +978,7 @@
         </ext>
       </extLst>
     </pivotField>
-    <pivotField showAll="0" includeNewItemsInFilter="1">
+    <pivotField numFmtId="2" showAll="0" includeNewItemsInFilter="1">
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
           <x14:pivotField fillDownLabels="1"/>
@@ -465,6 +992,13 @@
         </ext>
       </extLst>
     </pivotField>
+    <pivotField numFmtId="2" showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
     <pivotField showAll="0" includeNewItemsInFilter="1">
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
@@ -472,7 +1006,7 @@
         </ext>
       </extLst>
     </pivotField>
-    <pivotField showAll="0" includeNewItemsInFilter="1">
+    <pivotField numFmtId="22" showAll="0" includeNewItemsInFilter="1">
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
           <x14:pivotField fillDownLabels="1"/>
@@ -488,23 +1022,9 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="1"/>
+    <field x="0"/>
   </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="5">
+  <rowItems count="4">
     <i>
       <x/>
     </i>
@@ -514,15 +1034,15 @@
     <i>
       <x v="2"/>
     </i>
-    <i>
-      <x v="3"/>
-    </i>
     <i t="grand">
       <x/>
     </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Min of Galutinė kaina" fld="8" subtotal="min" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Galutinė kaina" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -799,7 +1319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{936E2D1B-75AA-4ED9-BCB5-CFD99655A6FC}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" customWidth="1"/>
@@ -812,17 +1332,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -832,7 +1342,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AF5DFFA-E62C-4233-BB43-6DED98E5A047}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" customWidth="1"/>
@@ -845,7 +1355,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -854,6 +1369,1333 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A82665-EBC7-4EEF-96D3-7BD8C72776F6}">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="3">
+        <v>21.79</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="2">
+        <v>46165.744849537034</v>
+      </c>
+      <c r="I2">
+        <v>25.689999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3">
+        <v>31.99</v>
+      </c>
+      <c r="E3" s="3">
+        <v>30.34</v>
+      </c>
+      <c r="F3" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="2">
+        <v>46165.744930555556</v>
+      </c>
+      <c r="I3">
+        <v>33.83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="3">
+        <v>31.99</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="3">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="2">
+        <v>46165.745011574072</v>
+      </c>
+      <c r="I4">
+        <v>37.989999999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="3">
+        <v>21.79</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="2">
+        <v>46165.730995370373</v>
+      </c>
+      <c r="I5">
+        <v>25.689999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>31.99</v>
+      </c>
+      <c r="E6" s="3">
+        <v>30.34</v>
+      </c>
+      <c r="F6" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="2">
+        <v>46165.731064814812</v>
+      </c>
+      <c r="I6">
+        <v>33.83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="3">
+        <v>31.99</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="3">
+        <v>6</v>
+      </c>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="2">
+        <v>46165.731134259258</v>
+      </c>
+      <c r="I7">
+        <v>37.989999999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="3">
+        <v>14.76</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="2">
+        <v>46165.731226851851</v>
+      </c>
+      <c r="I8">
+        <v>18.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="3">
+        <v>21.13</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="G9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="2">
+        <v>46165.731307870374</v>
+      </c>
+      <c r="I9">
+        <v>24.619999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="3">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="3">
+        <v>6</v>
+      </c>
+      <c r="G10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="2">
+        <v>46165.731388888889</v>
+      </c>
+      <c r="I10">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="3">
+        <v>155.99</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="2">
+        <v>46165.731481481482</v>
+      </c>
+      <c r="I11">
+        <v>159.89000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="3">
+        <v>189.99</v>
+      </c>
+      <c r="E12" s="3">
+        <v>155.85</v>
+      </c>
+      <c r="F12" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="G12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="2">
+        <v>46165.731550925928</v>
+      </c>
+      <c r="I12">
+        <v>159.34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="3">
+        <v>189.99</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="3">
+        <v>6</v>
+      </c>
+      <c r="G13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="2">
+        <v>46165.731631944444</v>
+      </c>
+      <c r="I13">
+        <v>195.99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="3">
+        <v>52.97</v>
+      </c>
+      <c r="E14" s="3">
+        <v>51.57</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="G14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="2">
+        <v>46165.731712962966</v>
+      </c>
+      <c r="I14">
+        <v>55.47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="3">
+        <v>49.95</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="G15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="2">
+        <v>46165.731793981482</v>
+      </c>
+      <c r="I15">
+        <v>53.440000000000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="3">
+        <v>46.99</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="3">
+        <v>6</v>
+      </c>
+      <c r="G16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="2">
+        <v>46165.731863425928</v>
+      </c>
+      <c r="I16">
+        <v>52.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="3">
+        <v>72.989999999999995</v>
+      </c>
+      <c r="E17" s="3">
+        <v>62.56</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="G17" t="s">
+        <v>38</v>
+      </c>
+      <c r="H17" s="2">
+        <v>46165.731944444444</v>
+      </c>
+      <c r="I17">
+        <v>66.460000000000008</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="3">
+        <v>87.99</v>
+      </c>
+      <c r="E18" s="3">
+        <v>75.56</v>
+      </c>
+      <c r="F18" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="G18" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="2">
+        <v>46165.732025462959</v>
+      </c>
+      <c r="I18">
+        <v>79.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="3">
+        <v>87.99</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="3">
+        <v>6</v>
+      </c>
+      <c r="G19" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="2">
+        <v>46165.732094907406</v>
+      </c>
+      <c r="I19">
+        <v>93.99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="3">
+        <v>155.99</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="G20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="2">
+        <v>46165.732210648152</v>
+      </c>
+      <c r="I20">
+        <v>159.89000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="3">
+        <v>189.99</v>
+      </c>
+      <c r="E21" s="3">
+        <v>155.85</v>
+      </c>
+      <c r="F21" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="G21" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="2">
+        <v>46165.73228009259</v>
+      </c>
+      <c r="I21">
+        <v>159.34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="3">
+        <v>189.99</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="3">
+        <v>6</v>
+      </c>
+      <c r="G22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="2">
+        <v>46165.732361111113</v>
+      </c>
+      <c r="I22">
+        <v>195.99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="3">
+        <v>48.99</v>
+      </c>
+      <c r="E23" s="3">
+        <v>40.99</v>
+      </c>
+      <c r="F23" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="G23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="2">
+        <v>46165.732442129629</v>
+      </c>
+      <c r="I23">
+        <v>44.89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="3">
+        <v>54.15</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="G24" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="2">
+        <v>46165.732534722221</v>
+      </c>
+      <c r="I24">
+        <v>57.64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="3">
+        <v>59.99</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="3">
+        <v>6</v>
+      </c>
+      <c r="G25" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="2">
+        <v>46165.732604166667</v>
+      </c>
+      <c r="I25">
+        <v>65.990000000000009</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="3">
+        <v>42.99</v>
+      </c>
+      <c r="E26" s="3">
+        <v>41.99</v>
+      </c>
+      <c r="F26" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="G26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="2">
+        <v>46165.732685185183</v>
+      </c>
+      <c r="I26">
+        <v>45.89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="3">
+        <v>54.99</v>
+      </c>
+      <c r="E27" s="3">
+        <v>41.9</v>
+      </c>
+      <c r="F27" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="G27" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" s="2">
+        <v>46165.732766203706</v>
+      </c>
+      <c r="I27">
+        <v>45.39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="3">
+        <v>54.99</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="3">
+        <v>6</v>
+      </c>
+      <c r="G28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H28" s="2">
+        <v>46165.732835648145</v>
+      </c>
+      <c r="I28">
+        <v>60.99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="3">
+        <v>72.989999999999995</v>
+      </c>
+      <c r="E29" s="3">
+        <v>67.989999999999995</v>
+      </c>
+      <c r="F29" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="G29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" s="2">
+        <v>46165.732916666668</v>
+      </c>
+      <c r="I29">
+        <v>71.89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="3">
+        <v>94.99</v>
+      </c>
+      <c r="E30" s="3">
+        <v>70</v>
+      </c>
+      <c r="F30" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="G30" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="2">
+        <v>46165.732986111114</v>
+      </c>
+      <c r="I30">
+        <v>73.489999999999995</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="3">
+        <v>94.99</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="3">
+        <v>6</v>
+      </c>
+      <c r="G31" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" s="2">
+        <v>46165.733067129629</v>
+      </c>
+      <c r="I31">
+        <v>100.99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58464371-7C24-42E3-A4DC-A9838908DB45}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>33.83</v>
+      </c>
+      <c r="C2">
+        <v>25.69</v>
+      </c>
+      <c r="D2">
+        <v>37.989999999999995</v>
+      </c>
+      <c r="E2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>33.83</v>
+      </c>
+      <c r="C3">
+        <v>25.689999999999998</v>
+      </c>
+      <c r="D3">
+        <v>37.989999999999995</v>
+      </c>
+      <c r="E3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>24.619999999999902</v>
+      </c>
+      <c r="C4">
+        <v>18.66</v>
+      </c>
+      <c r="D4">
+        <v>25.99</v>
+      </c>
+      <c r="E4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>159.34</v>
+      </c>
+      <c r="C5">
+        <v>159.89000000000001</v>
+      </c>
+      <c r="D5">
+        <v>195.99</v>
+      </c>
+      <c r="E5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>53.44</v>
+      </c>
+      <c r="C6">
+        <v>55.47</v>
+      </c>
+      <c r="D6">
+        <v>52.99</v>
+      </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>79.05</v>
+      </c>
+      <c r="C7">
+        <v>66.460000000000008</v>
+      </c>
+      <c r="D7">
+        <v>93.99</v>
+      </c>
+      <c r="E7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>159.34</v>
+      </c>
+      <c r="C8">
+        <v>159.89000000000001</v>
+      </c>
+      <c r="D8">
+        <v>195.99</v>
+      </c>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>57.64</v>
+      </c>
+      <c r="C9">
+        <v>44.89</v>
+      </c>
+      <c r="D9">
+        <v>65.990000000000009</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>45.39</v>
+      </c>
+      <c r="C10">
+        <v>45.89</v>
+      </c>
+      <c r="D10">
+        <v>60.99</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>73.489999999999995</v>
+      </c>
+      <c r="C11">
+        <v>71.89</v>
+      </c>
+      <c r="D11">
+        <v>100.99</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D947CF0E-4621-439B-9599-CF319F06FACE}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>57.64</v>
+      </c>
+      <c r="C2">
+        <v>44.89</v>
+      </c>
+      <c r="D2">
+        <v>65.990000000000009</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>73.489999999999995</v>
+      </c>
+      <c r="C3">
+        <v>71.89</v>
+      </c>
+      <c r="D3">
+        <v>100.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>24.619999999999902</v>
+      </c>
+      <c r="C4">
+        <v>18.66</v>
+      </c>
+      <c r="D4">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>33.83</v>
+      </c>
+      <c r="C5">
+        <v>25.689999999999998</v>
+      </c>
+      <c r="D5">
+        <v>37.989999999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>53.44</v>
+      </c>
+      <c r="C6">
+        <v>55.47</v>
+      </c>
+      <c r="D6">
+        <v>52.99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>79.05</v>
+      </c>
+      <c r="C7">
+        <v>66.460000000000008</v>
+      </c>
+      <c r="D7">
+        <v>93.99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>159.34</v>
+      </c>
+      <c r="C8">
+        <v>159.89000000000001</v>
+      </c>
+      <c r="D8">
+        <v>195.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>45.39</v>
+      </c>
+      <c r="C9">
+        <v>45.89</v>
+      </c>
+      <c r="D9">
+        <v>60.99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10">
+        <v>71.996999999999986</v>
+      </c>
+      <c r="C10">
+        <v>67.441999999999993</v>
+      </c>
+      <c r="D10">
+        <v>86.890000000000015</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E0866C-1D02-4161-B937-22768E10AD49}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>868.90000000000009</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>719.97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>674.42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5">
+        <v>2263.29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D797EC2-8ECA-4DB3-8F97-C4723F363B42}">
   <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -911,294 +2753,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="17.109375" customWidth="1"/>
-    <col min="8" max="8" width="20.5546875" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="19.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="6">
-        <v>145.38999999999999</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="4">
-        <v>3.9</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="2">
-        <v>46164.785868055558</v>
-      </c>
-      <c r="I2">
-        <v>149.29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="7">
-        <v>189.99</v>
-      </c>
-      <c r="E3" s="5">
-        <v>155.85</v>
-      </c>
-      <c r="F3" s="4">
-        <v>3.49</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="2">
-        <v>46164.78597222222</v>
-      </c>
-      <c r="I3">
-        <v>159.34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="7">
-        <v>189.99</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="4">
-        <v>6</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="2">
-        <v>46164.786099537036</v>
-      </c>
-      <c r="I4">
-        <v>195.99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D8" s="7"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="4"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D9" s="6"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D10" s="6"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D11" s="6"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D13" s="6"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="H13" s="2"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{566B54B6-DFC9-4980-8690-A319480957CA}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{F66EA076-1138-4AD7-8E12-86E78701A557}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{8DF5865D-8E6E-460E-B1E8-828202625CDA}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C1CC2D0-D9C9-4997-BBAE-0EEAAC63CBD1}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="10">
-        <v>195.99</v>
-      </c>
-      <c r="C3" s="10">
-        <v>159.34</v>
-      </c>
-      <c r="D3" s="10">
-        <v>149.29</v>
-      </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10">
-        <v>149.29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="10">
-        <v>195.99</v>
-      </c>
-      <c r="C5" s="10">
-        <v>159.34</v>
-      </c>
-      <c r="D5" s="10">
-        <v>149.29</v>
-      </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10">
-        <v>149.29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Grupinis/KainuStebejimas.xlsx
+++ b/Grupinis/KainuStebejimas.xlsx
@@ -8,23 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vejas\OneDrive\Documents\UiPath\RPA\Grupinis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4579772-635D-45BB-9784-D6C9B9D95AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9DDC95-F65A-43D2-87E4-5731BBF83D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parduotuvės" sheetId="2" r:id="rId1"/>
     <sheet name="Prekės" sheetId="3" r:id="rId2"/>
     <sheet name="Kainos" sheetId="5" r:id="rId3"/>
-    <sheet name="Pigiausia" sheetId="6" r:id="rId4"/>
+    <sheet name="Geriausia kaina" sheetId="6" r:id="rId4"/>
     <sheet name="Kainų suvestinė" sheetId="7" r:id="rId5"/>
     <sheet name="Pardavėjų vertinimas" sheetId="8" r:id="rId6"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Kainos!$A$1:$I$31</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId8"/>
-    <pivotCache cacheId="1" r:id="rId9"/>
+    <pivotCache cacheId="3" r:id="rId8"/>
+    <pivotCache cacheId="7" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="81">
   <si>
     <t>Parduotuvė</t>
   </si>
@@ -81,40 +84,61 @@
     <t>Prekė</t>
   </si>
   <si>
+    <t>pigu.lt</t>
+  </si>
+  <si>
+    <t>Nuoroda</t>
+  </si>
+  <si>
+    <t>Įprasta kaina</t>
+  </si>
+  <si>
+    <t>Kaina su nuolaida</t>
+  </si>
+  <si>
+    <t>Siuntimo kaina</t>
+  </si>
+  <si>
+    <t>Ar prekė yra?</t>
+  </si>
+  <si>
+    <t>Tikrinimo laikas</t>
+  </si>
+  <si>
+    <t>Galutinė kaina</t>
+  </si>
+  <si>
+    <t>LEGO 77240</t>
+  </si>
+  <si>
     <t>varle.lt</t>
   </si>
   <si>
-    <t>pigu.lt</t>
-  </si>
-  <si>
     <t>lego.com</t>
   </si>
   <si>
-    <t>Nuoroda</t>
-  </si>
-  <si>
-    <t>Įprasta kaina</t>
-  </si>
-  <si>
-    <t>Kaina su nuolaida</t>
-  </si>
-  <si>
-    <t>Siuntimo kaina</t>
-  </si>
-  <si>
-    <t>Ar prekė yra?</t>
-  </si>
-  <si>
-    <t>Tikrinimo laikas</t>
-  </si>
-  <si>
-    <t>Galutinė kaina</t>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-creator-egzotiska-papuga-31136?id=68618776</t>
+  </si>
+  <si>
+    <t>Yra</t>
+  </si>
+  <si>
+    <t>https://www.varle.lt/lego/lego-creator-exotic-parrot--22946745.html</t>
   </si>
   <si>
     <t>Nėra</t>
   </si>
   <si>
-    <t>Yra</t>
+    <t>Liko tik: 4 vnt.</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/en-lt/product/exotic-parrot-31136</t>
+  </si>
+  <si>
+    <t>Limit 5</t>
+  </si>
+  <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-zydintis-kaktusas-11509?id=249971577</t>
   </si>
   <si>
     <t>https://www.varle.lt/lego/lego-botanicals-zydintis-kaktusas-augalu-dekoras--50745550.html</t>
@@ -123,78 +147,90 @@
     <t>Liko tik: 5+ vnt.</t>
   </si>
   <si>
-    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-zydintis-kaktusas-11509?id=249971577</t>
-  </si>
-  <si>
     <t>https://www.lego.com/en-lt/product/flowering-cactus-11509</t>
   </si>
   <si>
+    <t>Limit 3</t>
+  </si>
+  <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-besisupantys-augalai-geliu-rinkinys-11506?id=256483817</t>
+  </si>
+  <si>
     <t>https://www.varle.lt/lego/lego-besisupantys-augalai--53770717.html</t>
   </si>
   <si>
-    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-besisupantys-augalai-geliu-rinkinys-11506?id=256483817</t>
-  </si>
-  <si>
     <t>https://www.lego.com/en-lt/product/rocking-plants-11506</t>
   </si>
   <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-editions-football-fifa-world-cup-oficiali?id=254734272</t>
+  </si>
+  <si>
     <t>https://www.varle.lt/lego/lego-editions-fifa-world-cuptm-oficiali-taure--50253636.html</t>
   </si>
   <si>
     <t>Liko tik: 3 vnt.</t>
   </si>
   <si>
-    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-editions-football-fifa-world-cup-oficiali?id=254734272</t>
-  </si>
-  <si>
     <t>https://www.lego.com/en-lt/product/fifa-world-cup-official-trophy-43020</t>
   </si>
   <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-minecraft-lape-21588?id=249971612</t>
+  </si>
+  <si>
     <t>https://www.varle.lt/robotai-ismanus-zaislai/lego-minecraft-lis-21588--53525886.html</t>
   </si>
   <si>
-    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-minecraft-lape-21588?id=249971612</t>
-  </si>
-  <si>
     <t>https://www.lego.com/en-lt/product/the-fox-21588</t>
   </si>
   <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-art-love-31214?id=116946294</t>
+  </si>
+  <si>
     <t>https://www.varle.lt/lego/lego-art-love-31214--41770074.html</t>
   </si>
   <si>
     <t>Liko tik: 2 vnt.</t>
   </si>
   <si>
-    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-art-love-31214?id=116946294</t>
-  </si>
-  <si>
     <t>https://www.lego.com/en-lt/product/love-31214</t>
   </si>
   <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/77240-lego-speed-champions-sportinis-hiperautomobilis-bugatti?id=241505891</t>
+  </si>
+  <si>
+    <t>https://www.varle.lt/lego/lego-speed-champions-sportinis-hiperautomobilis-bugatti--46731151.html</t>
+  </si>
+  <si>
+    <t>Liko tik: 1 vnt.</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/en-lt/product/bugatti-centodieci-hyper-sports-car-77240</t>
+  </si>
+  <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-bonsai-medelis-10281?id=36407853</t>
+  </si>
+  <si>
     <t>https://www.varle.lt/lego/lego-icons-bonsai-medelis-10281--15106778.html</t>
   </si>
   <si>
-    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-bonsai-medelis-10281?id=36407853</t>
-  </si>
-  <si>
     <t>https://www.lego.com/en-lt/product/bonsai-tree-10281</t>
   </si>
   <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/76443-lego-harry-potter-hagrido-ir-hario?id=125603664</t>
+  </si>
+  <si>
     <t>https://www.varle.lt/lego/lego-harry-potter-hagrido-ir-hario-pasivazinejimas--41842791.html</t>
   </si>
   <si>
-    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/76443-lego-harry-potter-hagrido-ir-hario?id=125603664</t>
-  </si>
-  <si>
     <t>https://www.lego.com/en-lt/product/hagrid-harrys-motorcycle-ride-76443</t>
   </si>
   <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-icons-mclaren-mp44-ir-ayrton-senna?id=80634865</t>
+  </si>
+  <si>
     <t>https://www.varle.lt/lego/lego-icons-mclaren-mp44-ir-ayrton-senna-10330--32593893.html</t>
   </si>
   <si>
-    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-icons-mclaren-mp44-ir-ayrton-senna?id=80634865</t>
-  </si>
-  <si>
     <t>https://www.lego.com/en-lt/product/mclaren-mp44-ayrton-senna-10330</t>
   </si>
   <si>
@@ -207,10 +243,10 @@
     <t>Lego.com</t>
   </si>
   <si>
-    <t>Pigiausia</t>
-  </si>
-  <si>
-    <t>varle.lt - 25.689999999999998</t>
+    <t>pigu.lt - 21.6</t>
+  </si>
+  <si>
+    <t>varle.lt - 25.69</t>
   </si>
   <si>
     <t>varle.lt - 18.66</t>
@@ -222,7 +258,10 @@
     <t>lego.com - 52.99</t>
   </si>
   <si>
-    <t>varle.lt - 66.46000000000001</t>
+    <t>varle.lt - 66.46</t>
+  </si>
+  <si>
+    <t>pigu.lt - 25.259999999999998</t>
   </si>
   <si>
     <t>varle.lt - 44.89</t>
@@ -252,10 +291,7 @@
     <t>Sum of Galutinė kaina</t>
   </si>
   <si>
-    <t>varle.lt - 25.69</t>
-  </si>
-  <si>
-    <t>aaaaaaaaasfdasdasdasdasomdasldpmasdopamsd</t>
+    <t>Geriausia kaina</t>
   </si>
 </sst>
 </file>
@@ -308,7 +344,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -320,6 +356,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -339,28 +377,30 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46165.745033680556" createdVersion="1" refreshedVersion="8" recordCount="10" xr:uid="{8ACD45B7-58CD-4D19-B6F1-AB000FB66EE0}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46165.837533680555" createdVersion="1" refreshedVersion="8" recordCount="10" xr:uid="{29438EEF-739B-4E41-88FD-1B529C0690AC}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:E11" sheet="Pigiausia"/>
+    <worksheetSource ref="A1:E11" sheet="Geriausia kaina"/>
   </cacheSource>
   <cacheFields count="5">
     <cacheField name="Prekė" numFmtId="0">
-      <sharedItems count="8">
+      <sharedItems count="10">
+        <s v="LEGO 31136"/>
         <s v="LEGO 11509"/>
         <s v="LEGO 11506"/>
         <s v="LEGO 43020"/>
         <s v="LEGO 21588"/>
         <s v="LEGO 31214"/>
+        <s v="LEGO 77240"/>
         <s v="LEGO 10281"/>
         <s v="LEGO 76443"/>
         <s v="LEGO 10330"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Pigu.lt" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="24.619999999999902" maxValue="159.34"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="21.6" maxValue="159.34"/>
     </cacheField>
     <cacheField name="Varle.lt" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="18.66" maxValue="159.89000000000001"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="18.66" maxValue="159.88999999999999"/>
     </cacheField>
     <cacheField name="Lego.com" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="25.99" maxValue="195.99"/>
@@ -378,15 +418,15 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46165.745051967591" createdVersion="1" refreshedVersion="8" recordCount="30" xr:uid="{35F765EF-BAEA-45AC-929D-E2C85667C430}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46165.837549305557" createdVersion="1" refreshedVersion="8" recordCount="30" xr:uid="{243E1128-2E91-4806-9DB7-E36B957A749F}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:I31" sheet="Kainos"/>
   </cacheSource>
   <cacheFields count="9">
     <cacheField name="Parduotuvė" numFmtId="0">
       <sharedItems count="3">
+        <s v="pigu.lt"/>
         <s v="varle.lt"/>
-        <s v="pigu.lt"/>
         <s v="lego.com"/>
       </sharedItems>
     </cacheField>
@@ -400,7 +440,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="14.76" maxValue="189.99"/>
     </cacheField>
     <cacheField name="Kaina su nuolaida" numFmtId="2">
-      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="30.34" maxValue="155.85"/>
+      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="18.11" maxValue="155.85"/>
     </cacheField>
     <cacheField name="Siuntimo kaina" numFmtId="2">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.49" maxValue="6"/>
@@ -409,7 +449,7 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Tikrinimo laikas" numFmtId="22">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-23T17:32:38" maxDate="2026-05-23T17:52:49"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-23T20:01:37" maxDate="2026-05-23T20:06:00"/>
     </cacheField>
     <cacheField name="Galutinė kaina" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="18.66" maxValue="195.99"/>
@@ -427,69 +467,69 @@
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="10">
   <r>
     <x v="0"/>
+    <n v="21.6"/>
+    <n v="22.47"/>
+    <n v="32.989999999999995"/>
+    <s v="pigu.lt - 21.6"/>
+  </r>
+  <r>
+    <x v="1"/>
     <n v="33.83"/>
     <n v="25.69"/>
     <n v="37.989999999999995"/>
     <s v="varle.lt - 25.69"/>
   </r>
   <r>
-    <x v="0"/>
-    <n v="33.83"/>
-    <n v="25.689999999999998"/>
-    <n v="37.989999999999995"/>
-    <s v="varle.lt - 25.689999999999998"/>
-  </r>
-  <r>
-    <x v="1"/>
+    <x v="2"/>
     <n v="24.619999999999902"/>
     <n v="18.66"/>
     <n v="25.99"/>
     <s v="varle.lt - 18.66"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="3"/>
     <n v="159.34"/>
-    <n v="159.89000000000001"/>
+    <n v="159.88999999999999"/>
     <n v="195.99"/>
     <s v="pigu.lt - 159.34"/>
   </r>
   <r>
-    <x v="3"/>
+    <x v="4"/>
     <n v="53.44"/>
     <n v="55.47"/>
     <n v="52.99"/>
     <s v="lego.com - 52.99"/>
   </r>
   <r>
-    <x v="4"/>
+    <x v="5"/>
     <n v="79.05"/>
-    <n v="66.460000000000008"/>
+    <n v="66.459999999999994"/>
     <n v="93.99"/>
-    <s v="varle.lt - 66.46000000000001"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <n v="159.34"/>
-    <n v="159.89000000000001"/>
-    <n v="195.99"/>
-    <s v="pigu.lt - 159.34"/>
-  </r>
-  <r>
-    <x v="5"/>
+    <s v="varle.lt - 66.46"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="25.259999999999899"/>
+    <n v="25.68"/>
+    <n v="35.989999999999995"/>
+    <s v="pigu.lt - 25.259999999999998"/>
+  </r>
+  <r>
+    <x v="7"/>
     <n v="57.64"/>
     <n v="44.89"/>
     <n v="65.990000000000009"/>
     <s v="varle.lt - 44.89"/>
   </r>
   <r>
-    <x v="6"/>
+    <x v="8"/>
     <n v="45.39"/>
     <n v="45.89"/>
-    <n v="60.99"/>
+    <n v="49.99"/>
     <s v="pigu.lt - 45.39"/>
   </r>
   <r>
-    <x v="7"/>
+    <x v="9"/>
     <n v="73.489999999999995"/>
     <n v="71.89"/>
     <n v="100.99"/>
@@ -502,25 +542,58 @@
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="30">
   <r>
     <x v="0"/>
+    <s v="LEGO 31136"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-creator-egzotiska-papuga-31136?id=68618776"/>
+    <n v="26.99"/>
+    <n v="18.11"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T20:01:37"/>
+    <n v="21.6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="LEGO 31136"/>
+    <s v="https://www.varle.lt/lego/lego-creator-exotic-parrot--22946745.html"/>
+    <n v="18.57"/>
+    <s v="Nėra"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 4 vnt."/>
+    <d v="2026-05-23T20:01:46"/>
+    <n v="22.47"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="LEGO 31136"/>
+    <s v="https://www.lego.com/en-lt/product/exotic-parrot-31136"/>
+    <n v="26.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Limit 5"/>
+    <d v="2026-05-23T20:02:00"/>
+    <n v="32.989999999999995"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="LEGO 11509"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-zydintis-kaktusas-11509?id=249971577"/>
+    <n v="31.99"/>
+    <n v="30.34"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-23T20:02:08"/>
+    <n v="33.83"/>
+  </r>
+  <r>
+    <x v="1"/>
     <s v="LEGO 11509"/>
     <s v="https://www.varle.lt/lego/lego-botanicals-zydintis-kaktusas-augalu-dekoras--50745550.html"/>
     <n v="21.79"/>
     <s v="Nėra"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-23T17:52:35"/>
+    <d v="2026-05-23T20:02:17"/>
     <n v="25.689999999999998"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="LEGO 11509"/>
-    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-zydintis-kaktusas-11509?id=249971577"/>
-    <n v="31.99"/>
-    <n v="30.34"/>
-    <n v="3.49"/>
-    <s v="Yra"/>
-    <d v="2026-05-23T17:52:42"/>
-    <n v="33.83"/>
   </r>
   <r>
     <x v="2"/>
@@ -529,64 +602,31 @@
     <n v="31.99"/>
     <s v="Nėra"/>
     <n v="6"/>
-    <s v="Yra"/>
-    <d v="2026-05-23T17:52:49"/>
+    <s v="Limit 3"/>
+    <d v="2026-05-23T20:02:27"/>
     <n v="37.989999999999995"/>
   </r>
   <r>
     <x v="0"/>
-    <s v="LEGO 11509"/>
-    <s v="https://www.varle.lt/lego/lego-botanicals-zydintis-kaktusas-augalu-dekoras--50745550.html"/>
-    <n v="21.79"/>
+    <s v="LEGO 11506"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-besisupantys-augalai-geliu-rinkinys-11506?id=256483817"/>
+    <n v="21.13"/>
     <s v="Nėra"/>
-    <n v="3.9"/>
-    <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-23T17:32:38"/>
-    <n v="25.689999999999998"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="LEGO 11509"/>
-    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-zydintis-kaktusas-11509?id=249971577"/>
-    <n v="31.99"/>
-    <n v="30.34"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T17:32:44"/>
-    <n v="33.83"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <s v="LEGO 11509"/>
-    <s v="https://www.lego.com/en-lt/product/flowering-cactus-11509"/>
-    <n v="31.99"/>
-    <s v="Nėra"/>
-    <n v="6"/>
-    <s v="Yra"/>
-    <d v="2026-05-23T17:32:50"/>
-    <n v="37.989999999999995"/>
-  </r>
-  <r>
-    <x v="0"/>
+    <d v="2026-05-23T20:02:36"/>
+    <n v="24.619999999999997"/>
+  </r>
+  <r>
+    <x v="1"/>
     <s v="LEGO 11506"/>
     <s v="https://www.varle.lt/lego/lego-besisupantys-augalai--53770717.html"/>
     <n v="14.76"/>
     <s v="Nėra"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-23T17:32:58"/>
+    <d v="2026-05-23T20:02:44"/>
     <n v="18.66"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="LEGO 11506"/>
-    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-besisupantys-augalai-geliu-rinkinys-11506?id=256483817"/>
-    <n v="21.13"/>
-    <s v="Nėra"/>
-    <n v="3.49"/>
-    <s v="Yra"/>
-    <d v="2026-05-23T17:33:05"/>
-    <n v="24.619999999999997"/>
   </r>
   <r>
     <x v="2"/>
@@ -595,31 +635,31 @@
     <n v="19.989999999999998"/>
     <s v="Nėra"/>
     <n v="6"/>
+    <s v="Limit 3"/>
+    <d v="2026-05-23T20:02:57"/>
+    <n v="25.99"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="LEGO 43020"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-editions-football-fifa-world-cup-oficiali?id=254734272"/>
+    <n v="189.99"/>
+    <n v="155.85"/>
+    <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T17:33:12"/>
-    <n v="25.99"/>
-  </r>
-  <r>
-    <x v="0"/>
+    <d v="2026-05-23T20:03:05"/>
+    <n v="159.34"/>
+  </r>
+  <r>
+    <x v="1"/>
     <s v="LEGO 43020"/>
     <s v="https://www.varle.lt/lego/lego-editions-fifa-world-cuptm-oficiali-taure--50253636.html"/>
     <n v="155.99"/>
     <s v="Nėra"/>
     <n v="3.9"/>
     <s v="Liko tik: 3 vnt."/>
-    <d v="2026-05-23T17:33:20"/>
+    <d v="2026-05-23T20:03:14"/>
     <n v="159.89000000000001"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="LEGO 43020"/>
-    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-editions-football-fifa-world-cup-oficiali?id=254734272"/>
-    <n v="189.99"/>
-    <n v="155.85"/>
-    <n v="3.49"/>
-    <s v="Yra"/>
-    <d v="2026-05-23T17:33:26"/>
-    <n v="159.34"/>
   </r>
   <r>
     <x v="2"/>
@@ -628,31 +668,31 @@
     <n v="189.99"/>
     <s v="Nėra"/>
     <n v="6"/>
+    <s v="Limit 3"/>
+    <d v="2026-05-23T20:03:24"/>
+    <n v="195.99"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="LEGO 21588"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-minecraft-lape-21588?id=249971612"/>
+    <n v="49.95"/>
+    <s v="Nėra"/>
+    <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T17:33:33"/>
-    <n v="195.99"/>
-  </r>
-  <r>
-    <x v="0"/>
+    <d v="2026-05-23T20:03:33"/>
+    <n v="53.440000000000005"/>
+  </r>
+  <r>
+    <x v="1"/>
     <s v="LEGO 21588"/>
     <s v="https://www.varle.lt/robotai-ismanus-zaislai/lego-minecraft-lis-21588--53525886.html"/>
     <n v="52.97"/>
     <n v="51.57"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-23T17:33:40"/>
+    <d v="2026-05-23T20:03:41"/>
     <n v="55.47"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="LEGO 21588"/>
-    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-minecraft-lape-21588?id=249971612"/>
-    <n v="49.95"/>
-    <s v="Nėra"/>
-    <n v="3.49"/>
-    <s v="Yra"/>
-    <d v="2026-05-23T17:33:47"/>
-    <n v="53.440000000000005"/>
   </r>
   <r>
     <x v="2"/>
@@ -661,31 +701,31 @@
     <n v="46.99"/>
     <s v="Nėra"/>
     <n v="6"/>
+    <s v="Limit 3"/>
+    <d v="2026-05-23T20:03:52"/>
+    <n v="52.99"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="LEGO 31214"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-art-love-31214?id=116946294"/>
+    <n v="87.99"/>
+    <n v="75.56"/>
+    <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T17:33:53"/>
-    <n v="52.99"/>
-  </r>
-  <r>
-    <x v="0"/>
+    <d v="2026-05-23T20:04:00"/>
+    <n v="79.05"/>
+  </r>
+  <r>
+    <x v="1"/>
     <s v="LEGO 31214"/>
     <s v="https://www.varle.lt/lego/lego-art-love-31214--41770074.html"/>
     <n v="72.989999999999995"/>
     <n v="62.56"/>
     <n v="3.9"/>
     <s v="Liko tik: 2 vnt."/>
-    <d v="2026-05-23T17:34:00"/>
+    <d v="2026-05-23T20:04:08"/>
     <n v="66.460000000000008"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="LEGO 31214"/>
-    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-art-love-31214?id=116946294"/>
-    <n v="87.99"/>
-    <n v="75.56"/>
-    <n v="3.49"/>
-    <s v="Yra"/>
-    <d v="2026-05-23T17:34:07"/>
-    <n v="79.05"/>
   </r>
   <r>
     <x v="2"/>
@@ -694,64 +734,64 @@
     <n v="87.99"/>
     <s v="Nėra"/>
     <n v="6"/>
+    <s v="Limit 3"/>
+    <d v="2026-05-23T20:04:19"/>
+    <n v="93.99"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="LEGO 77240"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/77240-lego-speed-champions-sportinis-hiperautomobilis-bugatti?id=241505891"/>
+    <n v="29.99"/>
+    <n v="21.77"/>
+    <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T17:34:13"/>
-    <n v="93.99"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <s v="LEGO 43020"/>
-    <s v="https://www.varle.lt/lego/lego-editions-fifa-world-cuptm-oficiali-taure--50253636.html"/>
-    <n v="155.99"/>
+    <d v="2026-05-23T20:04:27"/>
+    <n v="25.259999999999998"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="LEGO 77240"/>
+    <s v="https://www.varle.lt/lego/lego-speed-champions-sportinis-hiperautomobilis-bugatti--46731151.html"/>
+    <n v="21.78"/>
     <s v="Nėra"/>
     <n v="3.9"/>
-    <s v="Liko tik: 3 vnt."/>
-    <d v="2026-05-23T17:34:23"/>
-    <n v="159.89000000000001"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="LEGO 43020"/>
-    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-editions-football-fifa-world-cup-oficiali?id=254734272"/>
-    <n v="189.99"/>
-    <n v="155.85"/>
+    <s v="Liko tik: 1 vnt."/>
+    <d v="2026-05-23T20:04:36"/>
+    <n v="25.68"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="LEGO 77240"/>
+    <s v="https://www.lego.com/en-lt/product/bugatti-centodieci-hyper-sports-car-77240"/>
+    <n v="29.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Limit 3"/>
+    <d v="2026-05-23T20:04:47"/>
+    <n v="35.989999999999995"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="LEGO 10281"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-bonsai-medelis-10281?id=36407853"/>
+    <n v="54.15"/>
+    <s v="Nėra"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T17:34:29"/>
-    <n v="159.34"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <s v="LEGO 43020"/>
-    <s v="https://www.lego.com/en-lt/product/fifa-world-cup-official-trophy-43020"/>
-    <n v="189.99"/>
-    <s v="Nėra"/>
-    <n v="6"/>
-    <s v="Yra"/>
-    <d v="2026-05-23T17:34:36"/>
-    <n v="195.99"/>
-  </r>
-  <r>
-    <x v="0"/>
+    <d v="2026-05-23T20:04:55"/>
+    <n v="57.64"/>
+  </r>
+  <r>
+    <x v="1"/>
     <s v="LEGO 10281"/>
     <s v="https://www.varle.lt/lego/lego-icons-bonsai-medelis-10281--15106778.html"/>
     <n v="48.99"/>
     <n v="40.99"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-23T17:34:43"/>
+    <d v="2026-05-23T20:05:05"/>
     <n v="44.89"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="LEGO 10281"/>
-    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-bonsai-medelis-10281?id=36407853"/>
-    <n v="54.15"/>
-    <s v="Nėra"/>
-    <n v="3.49"/>
-    <s v="Yra"/>
-    <d v="2026-05-23T17:34:51"/>
-    <n v="57.64"/>
   </r>
   <r>
     <x v="2"/>
@@ -760,64 +800,64 @@
     <n v="59.99"/>
     <s v="Nėra"/>
     <n v="6"/>
+    <s v="Limit 5"/>
+    <d v="2026-05-23T20:05:14"/>
+    <n v="65.990000000000009"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="LEGO 76443"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/76443-lego-harry-potter-hagrido-ir-hario?id=125603664"/>
+    <n v="54.99"/>
+    <n v="41.9"/>
+    <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T17:34:57"/>
-    <n v="65.990000000000009"/>
-  </r>
-  <r>
-    <x v="0"/>
+    <d v="2026-05-23T20:05:20"/>
+    <n v="45.39"/>
+  </r>
+  <r>
+    <x v="1"/>
     <s v="LEGO 76443"/>
     <s v="https://www.varle.lt/lego/lego-harry-potter-hagrido-ir-hario-pasivazinejimas--41842791.html"/>
     <n v="42.99"/>
     <n v="41.99"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-23T17:35:04"/>
+    <d v="2026-05-23T20:05:27"/>
     <n v="45.89"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="LEGO 76443"/>
-    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/76443-lego-harry-potter-hagrido-ir-hario?id=125603664"/>
-    <n v="54.99"/>
-    <n v="41.9"/>
-    <n v="3.49"/>
-    <s v="Yra"/>
-    <d v="2026-05-23T17:35:11"/>
-    <n v="45.39"/>
   </r>
   <r>
     <x v="2"/>
     <s v="LEGO 76443"/>
     <s v="https://www.lego.com/en-lt/product/hagrid-harrys-motorcycle-ride-76443"/>
     <n v="54.99"/>
-    <s v="Nėra"/>
+    <n v="43.99"/>
     <n v="6"/>
+    <s v="Limit 5"/>
+    <d v="2026-05-23T20:05:36"/>
+    <n v="49.99"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="LEGO 10330"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-icons-mclaren-mp44-ir-ayrton-senna?id=80634865"/>
+    <n v="94.99"/>
+    <n v="70"/>
+    <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T17:35:17"/>
-    <n v="60.99"/>
-  </r>
-  <r>
-    <x v="0"/>
+    <d v="2026-05-23T20:05:43"/>
+    <n v="73.489999999999995"/>
+  </r>
+  <r>
+    <x v="1"/>
     <s v="LEGO 10330"/>
     <s v="https://www.varle.lt/lego/lego-icons-mclaren-mp44-ir-ayrton-senna-10330--32593893.html"/>
     <n v="72.989999999999995"/>
     <n v="67.989999999999995"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-23T17:35:24"/>
+    <d v="2026-05-23T20:05:50"/>
     <n v="71.89"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="LEGO 10330"/>
-    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-icons-mclaren-mp44-ir-ayrton-senna?id=80634865"/>
-    <n v="94.99"/>
-    <n v="70"/>
-    <n v="3.49"/>
-    <s v="Yra"/>
-    <d v="2026-05-23T17:35:30"/>
-    <n v="73.489999999999995"/>
   </r>
   <r>
     <x v="2"/>
@@ -826,26 +866,28 @@
     <n v="94.99"/>
     <s v="Nėra"/>
     <n v="6"/>
-    <s v="Yra"/>
-    <d v="2026-05-23T17:35:37"/>
+    <s v="Limit 5"/>
+    <d v="2026-05-23T20:06:00"/>
     <n v="100.99"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BC89E6C5-8E2C-4B47-BFC3-3A55CB5A3665}" name="Vidutinė kaina" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
-  <location ref="A1:D10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{324A5369-8D7E-4AC2-B0C9-216B4A05F38D}" name="Vidutinė kaina" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
+  <location ref="A1:D12" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
-      <items count="9">
+      <items count="11">
+        <item x="7"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="0"/>
         <item x="5"/>
-        <item x="7"/>
-        <item x="1"/>
-        <item x="0"/>
         <item x="3"/>
-        <item x="4"/>
-        <item x="2"/>
+        <item x="8"/>
         <item x="6"/>
         <item t="default"/>
       </items>
@@ -887,7 +929,7 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="9">
+  <rowItems count="11">
     <i>
       <x/>
     </i>
@@ -911,6 +953,12 @@
     </i>
     <i>
       <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
     </i>
     <i t="grand">
       <x/>
@@ -948,14 +996,14 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C8789DDD-3966-48A0-93FD-759D3D65D707}" name="Parduotuvių vertinimas" cacheId="1" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24EA9CFE-ACCA-407D-AB1D-80979A8369A1}" name="Parduotuvių vertinimas" cacheId="7" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
   <location ref="A1:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
       <items count="4">
         <item x="2"/>
+        <item x="0"/>
         <item x="1"/>
-        <item x="0"/>
         <item t="default"/>
       </items>
       <extLst>
@@ -1319,7 +1367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{936E2D1B-75AA-4ED9-BCB5-CFD99655A6FC}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" customWidth="1"/>
@@ -1332,7 +1380,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1342,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AF5DFFA-E62C-4233-BB43-6DED98E5A047}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" customWidth="1"/>
@@ -1360,7 +1418,47 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1378,6 +1476,7 @@
     <col min="6" max="6" width="13.88671875" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="18.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -1388,25 +1487,25 @@
         <v>10</v>
       </c>
       <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>17</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>18</v>
-      </c>
-      <c r="H1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -1414,86 +1513,86 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="3">
+        <v>26.99</v>
+      </c>
+      <c r="E2" s="3">
+        <v>18.11</v>
+      </c>
+      <c r="F2" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="G2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="3">
-        <v>21.79</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="3">
-        <v>3.9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
       <c r="H2" s="2">
-        <v>46165.744849537034</v>
+        <v>46165.834456018521</v>
       </c>
       <c r="I2">
-        <v>25.689999999999998</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="3">
+        <v>18.57</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="3">
-        <v>31.99</v>
-      </c>
-      <c r="E3" s="3">
-        <v>30.34</v>
-      </c>
       <c r="F3" s="3">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H3" s="2">
-        <v>46165.744930555556</v>
+        <v>46165.834560185183</v>
       </c>
       <c r="I3">
-        <v>33.83</v>
+        <v>22.47</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3">
-        <v>31.99</v>
+        <v>26.99</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
         <v>6</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H4" s="2">
-        <v>46165.745011574072</v>
+        <v>46165.834722222222</v>
       </c>
       <c r="I4">
-        <v>37.989999999999995</v>
+        <v>32.989999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1504,80 +1603,80 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3">
+        <v>31.99</v>
+      </c>
+      <c r="E5" s="3">
+        <v>30.34</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="G5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="3">
-        <v>21.79</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="3">
-        <v>3.9</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
       <c r="H5" s="2">
-        <v>46165.730995370373</v>
+        <v>46165.834814814814</v>
       </c>
       <c r="I5">
-        <v>25.689999999999998</v>
+        <v>33.83</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
       </c>
       <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="3">
+        <v>21.79</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="3">
-        <v>31.99</v>
-      </c>
-      <c r="E6" s="3">
-        <v>30.34</v>
-      </c>
       <c r="F6" s="3">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H6" s="2">
-        <v>46165.731064814812</v>
+        <v>46165.834918981483</v>
       </c>
       <c r="I6">
-        <v>33.83</v>
+        <v>25.689999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D7" s="3">
         <v>31.99</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H7" s="2">
-        <v>46165.731134259258</v>
+        <v>46165.835034722222</v>
       </c>
       <c r="I7">
         <v>37.989999999999995</v>
@@ -1591,80 +1690,80 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D8" s="3">
-        <v>14.76</v>
+        <v>21.13</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>3.9</v>
+        <v>3.49</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H8" s="2">
-        <v>46165.731226851851</v>
+        <v>46165.835138888891</v>
       </c>
       <c r="I8">
-        <v>18.66</v>
+        <v>24.619999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D9" s="3">
-        <v>21.13</v>
+        <v>14.76</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H9" s="2">
-        <v>46165.731307870374</v>
+        <v>46165.835231481484</v>
       </c>
       <c r="I9">
-        <v>24.619999999999997</v>
+        <v>18.66</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D10" s="3">
         <v>19.989999999999998</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3">
         <v>6</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H10" s="2">
-        <v>46165.731388888889</v>
+        <v>46165.835381944446</v>
       </c>
       <c r="I10">
         <v>25.99</v>
@@ -1678,80 +1777,80 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D11" s="3">
-        <v>155.99</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>21</v>
+        <v>189.99</v>
+      </c>
+      <c r="E11" s="3">
+        <v>155.85</v>
       </c>
       <c r="F11" s="3">
-        <v>3.9</v>
+        <v>3.49</v>
       </c>
       <c r="G11" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H11" s="2">
-        <v>46165.731481481482</v>
+        <v>46165.835474537038</v>
       </c>
       <c r="I11">
-        <v>159.89000000000001</v>
+        <v>159.34</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D12" s="3">
-        <v>189.99</v>
-      </c>
-      <c r="E12" s="3">
-        <v>155.85</v>
+        <v>155.99</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="G12" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="H12" s="2">
-        <v>46165.731550925928</v>
+        <v>46165.835578703707</v>
       </c>
       <c r="I12">
-        <v>159.34</v>
+        <v>159.89000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D13" s="3">
         <v>189.99</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3">
         <v>6</v>
       </c>
       <c r="G13" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H13" s="2">
-        <v>46165.731631944444</v>
+        <v>46165.835694444446</v>
       </c>
       <c r="I13">
         <v>195.99</v>
@@ -1765,80 +1864,80 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D14" s="3">
-        <v>52.97</v>
-      </c>
-      <c r="E14" s="3">
-        <v>51.57</v>
+        <v>49.95</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>3.9</v>
+        <v>3.49</v>
       </c>
       <c r="G14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H14" s="2">
-        <v>46165.731712962966</v>
+        <v>46165.835798611108</v>
       </c>
       <c r="I14">
-        <v>55.47</v>
+        <v>53.440000000000005</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3">
-        <v>49.95</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>21</v>
+        <v>52.97</v>
+      </c>
+      <c r="E15" s="3">
+        <v>51.57</v>
       </c>
       <c r="F15" s="3">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="G15" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H15" s="2">
-        <v>46165.731793981482</v>
+        <v>46165.8358912037</v>
       </c>
       <c r="I15">
-        <v>53.440000000000005</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D16" s="3">
         <v>46.99</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
         <v>6</v>
       </c>
       <c r="G16" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H16" s="2">
-        <v>46165.731863425928</v>
+        <v>46165.836018518516</v>
       </c>
       <c r="I16">
         <v>52.99</v>
@@ -1852,80 +1951,80 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D17" s="3">
-        <v>72.989999999999995</v>
+        <v>87.99</v>
       </c>
       <c r="E17" s="3">
-        <v>62.56</v>
+        <v>75.56</v>
       </c>
       <c r="F17" s="3">
-        <v>3.9</v>
+        <v>3.49</v>
       </c>
       <c r="G17" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H17" s="2">
-        <v>46165.731944444444</v>
+        <v>46165.836111111108</v>
       </c>
       <c r="I17">
-        <v>66.460000000000008</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D18" s="3">
-        <v>87.99</v>
+        <v>72.989999999999995</v>
       </c>
       <c r="E18" s="3">
-        <v>75.56</v>
+        <v>62.56</v>
       </c>
       <c r="F18" s="3">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="G18" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2">
-        <v>46165.732025462959</v>
+        <v>46165.8362037037</v>
       </c>
       <c r="I18">
-        <v>79.05</v>
+        <v>66.460000000000008</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D19" s="3">
         <v>87.99</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
         <v>6</v>
       </c>
       <c r="G19" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H19" s="2">
-        <v>46165.732094907406</v>
+        <v>46165.836331018516</v>
       </c>
       <c r="I19">
         <v>93.99</v>
@@ -1936,86 +2035,86 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D20" s="3">
-        <v>155.99</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>21</v>
+        <v>29.99</v>
+      </c>
+      <c r="E20" s="3">
+        <v>21.77</v>
       </c>
       <c r="F20" s="3">
-        <v>3.9</v>
+        <v>3.49</v>
       </c>
       <c r="G20" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H20" s="2">
-        <v>46165.732210648152</v>
+        <v>46165.836423611108</v>
       </c>
       <c r="I20">
-        <v>159.89000000000001</v>
+        <v>25.259999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D21" s="3">
-        <v>189.99</v>
-      </c>
-      <c r="E21" s="3">
-        <v>155.85</v>
+        <v>21.78</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="G21" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="H21" s="2">
-        <v>46165.73228009259</v>
+        <v>46165.836527777778</v>
       </c>
       <c r="I21">
-        <v>159.34</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="D22" s="3">
-        <v>189.99</v>
+        <v>29.99</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
         <v>6</v>
       </c>
       <c r="G22" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H22" s="2">
-        <v>46165.732361111113</v>
+        <v>46165.836655092593</v>
       </c>
       <c r="I22">
-        <v>195.99</v>
+        <v>35.989999999999995</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -2026,80 +2125,80 @@
         <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D23" s="3">
-        <v>48.99</v>
-      </c>
-      <c r="E23" s="3">
-        <v>40.99</v>
+        <v>54.15</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>3.9</v>
+        <v>3.49</v>
       </c>
       <c r="G23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H23" s="2">
-        <v>46165.732442129629</v>
+        <v>46165.836747685185</v>
       </c>
       <c r="I23">
-        <v>44.89</v>
+        <v>57.64</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D24" s="3">
-        <v>54.15</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>21</v>
+        <v>48.99</v>
+      </c>
+      <c r="E24" s="3">
+        <v>40.99</v>
       </c>
       <c r="F24" s="3">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="G24" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H24" s="2">
-        <v>46165.732534722221</v>
+        <v>46165.836863425924</v>
       </c>
       <c r="I24">
-        <v>57.64</v>
+        <v>44.89</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D25" s="3">
         <v>59.99</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
         <v>6</v>
       </c>
       <c r="G25" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H25" s="2">
-        <v>46165.732604166667</v>
+        <v>46165.836967592593</v>
       </c>
       <c r="I25">
         <v>65.990000000000009</v>
@@ -2113,83 +2212,83 @@
         <v>7</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D26" s="3">
-        <v>42.99</v>
+        <v>54.99</v>
       </c>
       <c r="E26" s="3">
-        <v>41.99</v>
+        <v>41.9</v>
       </c>
       <c r="F26" s="3">
-        <v>3.9</v>
+        <v>3.49</v>
       </c>
       <c r="G26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H26" s="2">
-        <v>46165.732685185183</v>
+        <v>46165.837037037039</v>
       </c>
       <c r="I26">
-        <v>45.89</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D27" s="3">
-        <v>54.99</v>
+        <v>42.99</v>
       </c>
       <c r="E27" s="3">
-        <v>41.9</v>
+        <v>41.99</v>
       </c>
       <c r="F27" s="3">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="G27" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H27" s="2">
-        <v>46165.732766203706</v>
+        <v>46165.837118055555</v>
       </c>
       <c r="I27">
-        <v>45.39</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D28" s="3">
         <v>54.99</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>21</v>
+      <c r="E28" s="3">
+        <v>43.99</v>
       </c>
       <c r="F28" s="3">
         <v>6</v>
       </c>
       <c r="G28" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H28" s="2">
-        <v>46165.732835648145</v>
+        <v>46165.837222222224</v>
       </c>
       <c r="I28">
-        <v>60.99</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
@@ -2200,86 +2299,87 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D29" s="3">
-        <v>72.989999999999995</v>
+        <v>94.99</v>
       </c>
       <c r="E29" s="3">
-        <v>67.989999999999995</v>
+        <v>70</v>
       </c>
       <c r="F29" s="3">
-        <v>3.9</v>
+        <v>3.49</v>
       </c>
       <c r="G29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H29" s="2">
-        <v>46165.732916666668</v>
+        <v>46165.83730324074</v>
       </c>
       <c r="I29">
-        <v>71.89</v>
+        <v>73.489999999999995</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D30" s="3">
-        <v>94.99</v>
+        <v>72.989999999999995</v>
       </c>
       <c r="E30" s="3">
-        <v>70</v>
+        <v>67.989999999999995</v>
       </c>
       <c r="F30" s="3">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="G30" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H30" s="2">
-        <v>46165.732986111114</v>
+        <v>46165.837384259263</v>
       </c>
       <c r="I30">
-        <v>73.489999999999995</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D31" s="3">
         <v>94.99</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F31" s="3">
         <v>6</v>
       </c>
       <c r="G31" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H31" s="2">
-        <v>46165.733067129629</v>
+        <v>46165.837500000001</v>
       </c>
       <c r="I31">
         <v>100.99</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I31" xr:uid="{B1A82665-EBC7-4EEF-96D3-7BD8C72776F6}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2294,190 +2394,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" t="s">
-        <v>53</v>
+      <c r="B1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8">
+        <v>21.6</v>
+      </c>
+      <c r="C2" s="8">
+        <v>22.47</v>
+      </c>
+      <c r="D2" s="8">
+        <v>32.989999999999995</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B3" s="8">
         <v>33.83</v>
       </c>
-      <c r="C2">
+      <c r="C3" s="8">
         <v>25.69</v>
       </c>
-      <c r="D2">
+      <c r="D3" s="8">
         <v>37.989999999999995</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E3" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8">
+        <v>24.619999999999902</v>
+      </c>
+      <c r="C4" s="8">
+        <v>18.66</v>
+      </c>
+      <c r="D4" s="8">
+        <v>25.99</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="8">
+        <v>159.34</v>
+      </c>
+      <c r="C5" s="8">
+        <v>159.88999999999999</v>
+      </c>
+      <c r="D5" s="8">
+        <v>195.99</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8">
+        <v>53.44</v>
+      </c>
+      <c r="C6" s="8">
+        <v>55.47</v>
+      </c>
+      <c r="D6" s="8">
+        <v>52.99</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>33.83</v>
-      </c>
-      <c r="C3">
-        <v>25.689999999999998</v>
-      </c>
-      <c r="D3">
-        <v>37.989999999999995</v>
-      </c>
-      <c r="E3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>24.619999999999902</v>
-      </c>
-      <c r="C4">
-        <v>18.66</v>
-      </c>
-      <c r="D4">
-        <v>25.99</v>
-      </c>
-      <c r="E4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>159.34</v>
-      </c>
-      <c r="C5">
-        <v>159.89000000000001</v>
-      </c>
-      <c r="D5">
-        <v>195.99</v>
-      </c>
-      <c r="E5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>53.44</v>
-      </c>
-      <c r="C6">
-        <v>55.47</v>
-      </c>
-      <c r="D6">
-        <v>52.99</v>
-      </c>
-      <c r="E6" t="s">
-        <v>57</v>
-      </c>
-    </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="8">
         <v>79.05</v>
       </c>
-      <c r="C7">
-        <v>66.460000000000008</v>
-      </c>
-      <c r="D7">
+      <c r="C7" s="8">
+        <v>66.459999999999994</v>
+      </c>
+      <c r="D7" s="8">
         <v>93.99</v>
       </c>
-      <c r="E7" t="s">
-        <v>58</v>
+      <c r="E7" s="8" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>159.34</v>
-      </c>
-      <c r="C8">
-        <v>159.89000000000001</v>
-      </c>
-      <c r="D8">
-        <v>195.99</v>
-      </c>
-      <c r="E8" t="s">
-        <v>56</v>
+      <c r="A8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="8">
+        <v>25.259999999999899</v>
+      </c>
+      <c r="C8" s="8">
+        <v>25.68</v>
+      </c>
+      <c r="D8" s="8">
+        <v>35.989999999999995</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="8">
         <v>57.64</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="8">
         <v>44.89</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="8">
         <v>65.990000000000009</v>
       </c>
-      <c r="E9" t="s">
-        <v>59</v>
+      <c r="E9" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="8">
         <v>45.39</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="8">
         <v>45.89</v>
       </c>
-      <c r="D10">
-        <v>60.99</v>
-      </c>
-      <c r="E10" t="s">
-        <v>60</v>
+      <c r="D10" s="8">
+        <v>49.99</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="8">
         <v>73.489999999999995</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="8">
         <v>71.89</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="8">
         <v>100.99</v>
       </c>
-      <c r="E11" t="s">
-        <v>61</v>
+      <c r="E11" s="8" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2487,7 +2587,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D947CF0E-4621-439B-9599-CF319F06FACE}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -2498,29 +2598,29 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
         <v>57.64</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="7">
         <v>44.89</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="7">
         <v>65.990000000000009</v>
       </c>
     </row>
@@ -2528,13 +2628,13 @@
       <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="7">
         <v>73.489999999999995</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="7">
         <v>71.89</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="7">
         <v>100.99</v>
       </c>
     </row>
@@ -2542,13 +2642,13 @@
       <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>24.619999999999902</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="7">
         <v>18.66</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="7">
         <v>25.99</v>
       </c>
     </row>
@@ -2556,13 +2656,13 @@
       <c r="A5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>33.83</v>
       </c>
-      <c r="C5">
-        <v>25.689999999999998</v>
-      </c>
-      <c r="D5">
+      <c r="C5" s="7">
+        <v>25.69</v>
+      </c>
+      <c r="D5" s="7">
         <v>37.989999999999995</v>
       </c>
     </row>
@@ -2570,70 +2670,98 @@
       <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>53.44</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="7">
         <v>55.47</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="7">
         <v>52.99</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>79.05</v>
-      </c>
-      <c r="C7">
-        <v>66.460000000000008</v>
-      </c>
-      <c r="D7">
-        <v>93.99</v>
+        <v>9</v>
+      </c>
+      <c r="B7" s="7">
+        <v>21.6</v>
+      </c>
+      <c r="C7" s="7">
+        <v>22.47</v>
+      </c>
+      <c r="D7" s="7">
+        <v>32.989999999999995</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>159.34</v>
-      </c>
-      <c r="C8">
-        <v>159.89000000000001</v>
-      </c>
-      <c r="D8">
-        <v>195.99</v>
+        <v>4</v>
+      </c>
+      <c r="B8" s="7">
+        <v>79.05</v>
+      </c>
+      <c r="C8" s="7">
+        <v>66.459999999999994</v>
+      </c>
+      <c r="D8" s="7">
+        <v>93.99</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>45.39</v>
-      </c>
-      <c r="C9">
-        <v>45.89</v>
-      </c>
-      <c r="D9">
-        <v>60.99</v>
+        <v>5</v>
+      </c>
+      <c r="B9" s="7">
+        <v>159.34</v>
+      </c>
+      <c r="C9" s="7">
+        <v>159.88999999999999</v>
+      </c>
+      <c r="D9" s="7">
+        <v>195.99</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10">
-        <v>71.996999999999986</v>
-      </c>
-      <c r="C10">
-        <v>67.441999999999993</v>
-      </c>
-      <c r="D10">
-        <v>86.890000000000015</v>
+        <v>7</v>
+      </c>
+      <c r="B10" s="7">
+        <v>45.39</v>
+      </c>
+      <c r="C10" s="7">
+        <v>45.89</v>
+      </c>
+      <c r="D10" s="7">
+        <v>49.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="7">
+        <v>25.259999999999899</v>
+      </c>
+      <c r="C11" s="7">
+        <v>25.68</v>
+      </c>
+      <c r="D11" s="7">
+        <v>35.989999999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="7">
+        <v>57.365999999999971</v>
+      </c>
+      <c r="C12" s="7">
+        <v>53.698999999999991</v>
+      </c>
+      <c r="D12" s="7">
+        <v>69.290000000000006</v>
       </c>
     </row>
   </sheetData>
@@ -2652,42 +2780,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>868.90000000000009</v>
+        <v>21</v>
+      </c>
+      <c r="B2" s="7">
+        <v>692.90000000000009</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3">
-        <v>719.97</v>
+        <v>11</v>
+      </c>
+      <c r="B3" s="7">
+        <v>573.66</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4">
-        <v>674.42</v>
+        <v>20</v>
+      </c>
+      <c r="B4" s="7">
+        <v>536.99</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5">
-        <v>2263.29</v>
+        <v>75</v>
+      </c>
+      <c r="B5" s="7">
+        <v>1803.55</v>
       </c>
     </row>
   </sheetData>
@@ -2732,7 +2860,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">

--- a/Grupinis/KainuStebejimas.xlsx
+++ b/Grupinis/KainuStebejimas.xlsx
@@ -8,26 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vejas\OneDrive\Documents\UiPath\RPA\Grupinis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9DDC95-F65A-43D2-87E4-5731BBF83D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E83AD6-E79A-4B44-AA30-2284559FF451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parduotuvės" sheetId="2" r:id="rId1"/>
     <sheet name="Prekės" sheetId="3" r:id="rId2"/>
-    <sheet name="Kainos" sheetId="5" r:id="rId3"/>
-    <sheet name="Geriausia kaina" sheetId="6" r:id="rId4"/>
-    <sheet name="Kainų suvestinė" sheetId="7" r:id="rId5"/>
-    <sheet name="Pardavėjų vertinimas" sheetId="8" r:id="rId6"/>
+    <sheet name="raw_duom" sheetId="5" r:id="rId3"/>
+    <sheet name="Geriausia kaina" sheetId="12" r:id="rId4"/>
+    <sheet name="Parduotuvių vertinimas" sheetId="15" r:id="rId5"/>
+    <sheet name="Įprasta kaina" sheetId="13" r:id="rId6"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Kainos!$A$1:$I$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">raw_duom!$A$1:$I$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId8"/>
-    <pivotCache cacheId="7" r:id="rId9"/>
+    <pivotCache cacheId="15" r:id="rId8"/>
+    <pivotCache cacheId="19" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="79">
   <si>
     <t>Parduotuvė</t>
   </si>
@@ -168,9 +168,6 @@
     <t>https://www.varle.lt/lego/lego-editions-fifa-world-cuptm-oficiali-taure--50253636.html</t>
   </si>
   <si>
-    <t>Liko tik: 3 vnt.</t>
-  </si>
-  <si>
     <t>https://www.lego.com/en-lt/product/fifa-world-cup-official-trophy-43020</t>
   </si>
   <si>
@@ -207,9 +204,6 @@
     <t>https://www.lego.com/en-lt/product/bugatti-centodieci-hyper-sports-car-77240</t>
   </si>
   <si>
-    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-bonsai-medelis-10281?id=36407853</t>
-  </si>
-  <si>
     <t>https://www.varle.lt/lego/lego-icons-bonsai-medelis-10281--15106778.html</t>
   </si>
   <si>
@@ -261,9 +255,6 @@
     <t>varle.lt - 66.46</t>
   </si>
   <si>
-    <t>pigu.lt - 25.259999999999998</t>
-  </si>
-  <si>
     <t>varle.lt - 44.89</t>
   </si>
   <si>
@@ -279,19 +270,22 @@
     <t>Grand Total</t>
   </si>
   <si>
-    <t>Average of Pigu.lt</t>
-  </si>
-  <si>
-    <t>Average of Varle.lt</t>
-  </si>
-  <si>
-    <t>Average of Lego.com</t>
-  </si>
-  <si>
     <t>Sum of Galutinė kaina</t>
   </si>
   <si>
     <t>Geriausia kaina</t>
+  </si>
+  <si>
+    <t>Liko tik: 5 vnt.</t>
+  </si>
+  <si>
+    <t>Min of Įprasta kaina</t>
+  </si>
+  <si>
+    <t>https://pigu.lt/lt/daiktu-krepsiai/vitrina-dezute-lego-10281-bonsai-tree?id=224211668</t>
+  </si>
+  <si>
+    <t>pigu.lt - 25.26</t>
   </si>
 </sst>
 </file>
@@ -356,8 +350,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -377,11 +373,18 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46165.837533680555" createdVersion="1" refreshedVersion="8" recordCount="10" xr:uid="{29438EEF-739B-4E41-88FD-1B529C0690AC}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46166.591880671294" createdVersion="1" refreshedVersion="8" recordCount="30" xr:uid="{2A810F29-BDBE-4F1C-8E87-98012A743E31}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:E11" sheet="Geriausia kaina"/>
+    <worksheetSource ref="A1:I31" sheet="raw_duom"/>
   </cacheSource>
-  <cacheFields count="5">
+  <cacheFields count="9">
+    <cacheField name="Parduotuvė" numFmtId="0">
+      <sharedItems count="3">
+        <s v="pigu.lt"/>
+        <s v="varle.lt"/>
+        <s v="lego.com"/>
+      </sharedItems>
+    </cacheField>
     <cacheField name="Prekė" numFmtId="0">
       <sharedItems count="10">
         <s v="LEGO 31136"/>
@@ -396,17 +399,26 @@
         <s v="LEGO 10330"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Pigu.lt" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="21.6" maxValue="159.34"/>
+    <cacheField name="Nuoroda" numFmtId="0">
+      <sharedItems/>
     </cacheField>
-    <cacheField name="Varle.lt" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="18.66" maxValue="159.88999999999999"/>
+    <cacheField name="Įprasta kaina" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="14.76" maxValue="189.99"/>
     </cacheField>
-    <cacheField name="Lego.com" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="25.99" maxValue="195.99"/>
+    <cacheField name="Kaina su nuolaida" numFmtId="2">
+      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="18.11" maxValue="155.85"/>
     </cacheField>
-    <cacheField name="Pigiausia" numFmtId="0">
+    <cacheField name="Siuntimo kaina" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.49" maxValue="6"/>
+    </cacheField>
+    <cacheField name="Ar prekė yra?" numFmtId="0">
       <sharedItems/>
+    </cacheField>
+    <cacheField name="Tikrinimo laikas" numFmtId="22">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-24T14:07:06" maxDate="2026-05-24T14:12:17"/>
+    </cacheField>
+    <cacheField name="Galutinė kaina" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="18.66" maxValue="195.99"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -418,9 +430,9 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46165.837549305557" createdVersion="1" refreshedVersion="8" recordCount="30" xr:uid="{243E1128-2E91-4806-9DB7-E36B957A749F}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46166.59189560185" createdVersion="1" refreshedVersion="8" recordCount="30" xr:uid="{25781A37-DFF8-4C0E-A6EA-89211E685B83}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:I31" sheet="Kainos"/>
+    <worksheetSource ref="A1:I31" sheet="raw_duom"/>
   </cacheSource>
   <cacheFields count="9">
     <cacheField name="Parduotuvė" numFmtId="0">
@@ -449,9 +461,9 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Tikrinimo laikas" numFmtId="22">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-23T20:01:37" maxDate="2026-05-23T20:06:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-24T14:07:06" maxDate="2026-05-24T14:12:17"/>
     </cacheField>
-    <cacheField name="Galutinė kaina" numFmtId="0">
+    <cacheField name="Galutinė kaina" numFmtId="2">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="18.66" maxValue="195.99"/>
     </cacheField>
   </cacheFields>
@@ -464,76 +476,336 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="10">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="30">
   <r>
     <x v="0"/>
+    <x v="0"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-creator-egzotiska-papuga-31136?id=68618776"/>
+    <n v="26.99"/>
+    <n v="18.11"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-24T14:07:06"/>
     <n v="21.6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="https://www.varle.lt/lego/lego-creator-exotic-parrot--22946745.html"/>
+    <n v="18.57"/>
+    <s v="Nėra"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 4 vnt."/>
+    <d v="2026-05-24T14:07:19"/>
     <n v="22.47"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="https://www.lego.com/en-lt/product/exotic-parrot-31136"/>
+    <n v="26.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Limit 5"/>
+    <d v="2026-05-24T14:07:31"/>
     <n v="32.989999999999995"/>
-    <s v="pigu.lt - 21.6"/>
-  </r>
-  <r>
+  </r>
+  <r>
+    <x v="0"/>
     <x v="1"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-zydintis-kaktusas-11509?id=249971577"/>
+    <n v="31.99"/>
+    <n v="30.34"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-24T14:07:42"/>
     <n v="33.83"/>
-    <n v="25.69"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="https://www.varle.lt/lego/lego-botanicals-zydintis-kaktusas-augalu-dekoras--50745550.html"/>
+    <n v="21.79"/>
+    <s v="Nėra"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 5+ vnt."/>
+    <d v="2026-05-24T14:07:54"/>
+    <n v="25.689999999999998"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="https://www.lego.com/en-lt/product/flowering-cactus-11509"/>
+    <n v="31.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Limit 3"/>
+    <d v="2026-05-24T14:08:06"/>
     <n v="37.989999999999995"/>
-    <s v="varle.lt - 25.69"/>
-  </r>
-  <r>
+  </r>
+  <r>
+    <x v="0"/>
     <x v="2"/>
-    <n v="24.619999999999902"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-besisupantys-augalai-geliu-rinkinys-11506?id=256483817"/>
+    <n v="21.13"/>
+    <s v="Nėra"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-24T14:08:17"/>
+    <n v="24.619999999999997"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="https://www.varle.lt/lego/lego-besisupantys-augalai--53770717.html"/>
+    <n v="14.76"/>
+    <s v="Nėra"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 5 vnt."/>
+    <d v="2026-05-24T14:08:29"/>
     <n v="18.66"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="https://www.lego.com/en-lt/product/rocking-plants-11506"/>
+    <n v="19.989999999999998"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Limit 3"/>
+    <d v="2026-05-24T14:08:42"/>
     <n v="25.99"/>
-    <s v="varle.lt - 18.66"/>
-  </r>
-  <r>
+  </r>
+  <r>
+    <x v="0"/>
     <x v="3"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-editions-football-fifa-world-cup-oficiali?id=254734272"/>
+    <n v="189.99"/>
+    <n v="155.85"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-24T14:08:54"/>
     <n v="159.34"/>
-    <n v="159.88999999999999"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="https://www.varle.lt/lego/lego-editions-fifa-world-cuptm-oficiali-taure--50253636.html"/>
+    <n v="155.99"/>
+    <s v="Nėra"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 2 vnt."/>
+    <d v="2026-05-24T14:09:07"/>
+    <n v="159.89000000000001"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="https://www.lego.com/en-lt/product/fifa-world-cup-official-trophy-43020"/>
+    <n v="189.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Limit 3"/>
+    <d v="2026-05-24T14:09:20"/>
     <n v="195.99"/>
-    <s v="pigu.lt - 159.34"/>
-  </r>
-  <r>
+  </r>
+  <r>
+    <x v="0"/>
     <x v="4"/>
-    <n v="53.44"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-minecraft-lape-21588?id=249971612"/>
+    <n v="49.95"/>
+    <s v="Nėra"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-24T14:09:30"/>
+    <n v="53.440000000000005"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="https://www.varle.lt/robotai-ismanus-zaislai/lego-minecraft-lis-21588--53525886.html"/>
+    <n v="52.97"/>
+    <n v="51.57"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 5+ vnt."/>
+    <d v="2026-05-24T14:09:42"/>
     <n v="55.47"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <s v="https://www.lego.com/en-lt/product/the-fox-21588"/>
+    <n v="46.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Limit 3"/>
+    <d v="2026-05-24T14:09:54"/>
     <n v="52.99"/>
-    <s v="lego.com - 52.99"/>
-  </r>
-  <r>
+  </r>
+  <r>
+    <x v="0"/>
     <x v="5"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-art-love-31214?id=116946294"/>
+    <n v="87.99"/>
+    <n v="75.56"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-24T14:10:06"/>
     <n v="79.05"/>
-    <n v="66.459999999999994"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <s v="https://www.varle.lt/lego/lego-art-love-31214--41770074.html"/>
+    <n v="72.989999999999995"/>
+    <n v="62.56"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 2 vnt."/>
+    <d v="2026-05-24T14:10:18"/>
+    <n v="66.460000000000008"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <s v="https://www.lego.com/en-lt/product/love-31214"/>
+    <n v="87.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Limit 3"/>
+    <d v="2026-05-24T14:10:30"/>
     <n v="93.99"/>
-    <s v="varle.lt - 66.46"/>
-  </r>
-  <r>
+  </r>
+  <r>
+    <x v="0"/>
     <x v="6"/>
-    <n v="25.259999999999899"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/77240-lego-speed-champions-sportinis-hiperautomobilis-bugatti?id=241505891"/>
+    <n v="29.99"/>
+    <n v="21.77"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-24T14:10:42"/>
+    <n v="25.259999999999998"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <s v="https://www.varle.lt/lego/lego-speed-champions-sportinis-hiperautomobilis-bugatti--46731151.html"/>
+    <n v="21.78"/>
+    <s v="Nėra"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 1 vnt."/>
+    <d v="2026-05-24T14:10:53"/>
     <n v="25.68"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="https://www.lego.com/en-lt/product/bugatti-centodieci-hyper-sports-car-77240"/>
+    <n v="29.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Limit 3"/>
+    <d v="2026-05-24T14:11:06"/>
     <n v="35.989999999999995"/>
-    <s v="pigu.lt - 25.259999999999998"/>
-  </r>
-  <r>
+  </r>
+  <r>
+    <x v="0"/>
     <x v="7"/>
-    <n v="57.64"/>
+    <s v="https://pigu.lt/lt/daiktu-krepsiai/vitrina-dezute-lego-10281-bonsai-tree?id=224211668"/>
+    <n v="75.42"/>
+    <s v="Nėra"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-24T14:11:15"/>
+    <n v="78.91"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <s v="https://www.varle.lt/lego/lego-icons-bonsai-medelis-10281--15106778.html"/>
+    <n v="48.99"/>
+    <n v="40.99"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 5+ vnt."/>
+    <d v="2026-05-24T14:11:22"/>
     <n v="44.89"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="7"/>
+    <s v="https://www.lego.com/en-lt/product/bonsai-tree-10281"/>
+    <n v="59.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Limit 5"/>
+    <d v="2026-05-24T14:11:31"/>
     <n v="65.990000000000009"/>
-    <s v="varle.lt - 44.89"/>
-  </r>
-  <r>
+  </r>
+  <r>
+    <x v="0"/>
     <x v="8"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/76443-lego-harry-potter-hagrido-ir-hario?id=125603664"/>
+    <n v="54.99"/>
+    <n v="41.9"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-24T14:11:38"/>
     <n v="45.39"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <s v="https://www.varle.lt/lego/lego-harry-potter-hagrido-ir-hario-pasivazinejimas--41842791.html"/>
+    <n v="42.99"/>
+    <n v="41.99"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 5+ vnt."/>
+    <d v="2026-05-24T14:11:45"/>
     <n v="45.89"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="8"/>
+    <s v="https://www.lego.com/en-lt/product/hagrid-harrys-motorcycle-ride-76443"/>
+    <n v="54.99"/>
+    <n v="43.99"/>
+    <n v="6"/>
+    <s v="Limit 5"/>
+    <d v="2026-05-24T14:11:52"/>
     <n v="49.99"/>
-    <s v="pigu.lt - 45.39"/>
-  </r>
-  <r>
+  </r>
+  <r>
+    <x v="0"/>
     <x v="9"/>
+    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-icons-mclaren-mp44-ir-ayrton-senna?id=80634865"/>
+    <n v="94.99"/>
+    <n v="70"/>
+    <n v="3.49"/>
+    <s v="Yra"/>
+    <d v="2026-05-24T14:11:58"/>
     <n v="73.489999999999995"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <s v="https://www.varle.lt/lego/lego-icons-mclaren-mp44-ir-ayrton-senna-10330--32593893.html"/>
+    <n v="70.989999999999995"/>
+    <n v="67.989999999999995"/>
+    <n v="3.9"/>
+    <s v="Liko tik: 5+ vnt."/>
+    <d v="2026-05-24T14:12:06"/>
     <n v="71.89"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <s v="https://www.lego.com/en-lt/product/mclaren-mp44-ayrton-senna-10330"/>
+    <n v="94.99"/>
+    <s v="Nėra"/>
+    <n v="6"/>
+    <s v="Limit 5"/>
+    <d v="2026-05-24T14:12:17"/>
     <n v="100.99"/>
-    <s v="varle.lt - 71.89"/>
   </r>
 </pivotCacheRecords>
 </file>
@@ -548,7 +820,7 @@
     <n v="18.11"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T20:01:37"/>
+    <d v="2026-05-24T14:07:06"/>
     <n v="21.6"/>
   </r>
   <r>
@@ -559,7 +831,7 @@
     <s v="Nėra"/>
     <n v="3.9"/>
     <s v="Liko tik: 4 vnt."/>
-    <d v="2026-05-23T20:01:46"/>
+    <d v="2026-05-24T14:07:19"/>
     <n v="22.47"/>
   </r>
   <r>
@@ -570,7 +842,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 5"/>
-    <d v="2026-05-23T20:02:00"/>
+    <d v="2026-05-24T14:07:31"/>
     <n v="32.989999999999995"/>
   </r>
   <r>
@@ -581,7 +853,7 @@
     <n v="30.34"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T20:02:08"/>
+    <d v="2026-05-24T14:07:42"/>
     <n v="33.83"/>
   </r>
   <r>
@@ -592,7 +864,7 @@
     <s v="Nėra"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-23T20:02:17"/>
+    <d v="2026-05-24T14:07:54"/>
     <n v="25.689999999999998"/>
   </r>
   <r>
@@ -603,7 +875,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-23T20:02:27"/>
+    <d v="2026-05-24T14:08:06"/>
     <n v="37.989999999999995"/>
   </r>
   <r>
@@ -614,7 +886,7 @@
     <s v="Nėra"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T20:02:36"/>
+    <d v="2026-05-24T14:08:17"/>
     <n v="24.619999999999997"/>
   </r>
   <r>
@@ -624,8 +896,8 @@
     <n v="14.76"/>
     <s v="Nėra"/>
     <n v="3.9"/>
-    <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-23T20:02:44"/>
+    <s v="Liko tik: 5 vnt."/>
+    <d v="2026-05-24T14:08:29"/>
     <n v="18.66"/>
   </r>
   <r>
@@ -636,7 +908,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-23T20:02:57"/>
+    <d v="2026-05-24T14:08:42"/>
     <n v="25.99"/>
   </r>
   <r>
@@ -647,7 +919,7 @@
     <n v="155.85"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T20:03:05"/>
+    <d v="2026-05-24T14:08:54"/>
     <n v="159.34"/>
   </r>
   <r>
@@ -657,8 +929,8 @@
     <n v="155.99"/>
     <s v="Nėra"/>
     <n v="3.9"/>
-    <s v="Liko tik: 3 vnt."/>
-    <d v="2026-05-23T20:03:14"/>
+    <s v="Liko tik: 2 vnt."/>
+    <d v="2026-05-24T14:09:07"/>
     <n v="159.89000000000001"/>
   </r>
   <r>
@@ -669,7 +941,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-23T20:03:24"/>
+    <d v="2026-05-24T14:09:20"/>
     <n v="195.99"/>
   </r>
   <r>
@@ -680,7 +952,7 @@
     <s v="Nėra"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T20:03:33"/>
+    <d v="2026-05-24T14:09:30"/>
     <n v="53.440000000000005"/>
   </r>
   <r>
@@ -691,7 +963,7 @@
     <n v="51.57"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-23T20:03:41"/>
+    <d v="2026-05-24T14:09:42"/>
     <n v="55.47"/>
   </r>
   <r>
@@ -702,7 +974,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-23T20:03:52"/>
+    <d v="2026-05-24T14:09:54"/>
     <n v="52.99"/>
   </r>
   <r>
@@ -713,7 +985,7 @@
     <n v="75.56"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T20:04:00"/>
+    <d v="2026-05-24T14:10:06"/>
     <n v="79.05"/>
   </r>
   <r>
@@ -724,7 +996,7 @@
     <n v="62.56"/>
     <n v="3.9"/>
     <s v="Liko tik: 2 vnt."/>
-    <d v="2026-05-23T20:04:08"/>
+    <d v="2026-05-24T14:10:18"/>
     <n v="66.460000000000008"/>
   </r>
   <r>
@@ -735,7 +1007,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-23T20:04:19"/>
+    <d v="2026-05-24T14:10:30"/>
     <n v="93.99"/>
   </r>
   <r>
@@ -746,7 +1018,7 @@
     <n v="21.77"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T20:04:27"/>
+    <d v="2026-05-24T14:10:42"/>
     <n v="25.259999999999998"/>
   </r>
   <r>
@@ -757,7 +1029,7 @@
     <s v="Nėra"/>
     <n v="3.9"/>
     <s v="Liko tik: 1 vnt."/>
-    <d v="2026-05-23T20:04:36"/>
+    <d v="2026-05-24T14:10:53"/>
     <n v="25.68"/>
   </r>
   <r>
@@ -768,19 +1040,19 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-23T20:04:47"/>
+    <d v="2026-05-24T14:11:06"/>
     <n v="35.989999999999995"/>
   </r>
   <r>
     <x v="0"/>
     <s v="LEGO 10281"/>
-    <s v="https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-bonsai-medelis-10281?id=36407853"/>
-    <n v="54.15"/>
+    <s v="https://pigu.lt/lt/daiktu-krepsiai/vitrina-dezute-lego-10281-bonsai-tree?id=224211668"/>
+    <n v="75.42"/>
     <s v="Nėra"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T20:04:55"/>
-    <n v="57.64"/>
+    <d v="2026-05-24T14:11:15"/>
+    <n v="78.91"/>
   </r>
   <r>
     <x v="1"/>
@@ -790,7 +1062,7 @@
     <n v="40.99"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-23T20:05:05"/>
+    <d v="2026-05-24T14:11:22"/>
     <n v="44.89"/>
   </r>
   <r>
@@ -801,7 +1073,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 5"/>
-    <d v="2026-05-23T20:05:14"/>
+    <d v="2026-05-24T14:11:31"/>
     <n v="65.990000000000009"/>
   </r>
   <r>
@@ -812,7 +1084,7 @@
     <n v="41.9"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T20:05:20"/>
+    <d v="2026-05-24T14:11:38"/>
     <n v="45.39"/>
   </r>
   <r>
@@ -823,7 +1095,7 @@
     <n v="41.99"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-23T20:05:27"/>
+    <d v="2026-05-24T14:11:45"/>
     <n v="45.89"/>
   </r>
   <r>
@@ -834,7 +1106,7 @@
     <n v="43.99"/>
     <n v="6"/>
     <s v="Limit 5"/>
-    <d v="2026-05-23T20:05:36"/>
+    <d v="2026-05-24T14:11:52"/>
     <n v="49.99"/>
   </r>
   <r>
@@ -845,18 +1117,18 @@
     <n v="70"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-23T20:05:43"/>
+    <d v="2026-05-24T14:11:58"/>
     <n v="73.489999999999995"/>
   </r>
   <r>
     <x v="1"/>
     <s v="LEGO 10330"/>
     <s v="https://www.varle.lt/lego/lego-icons-mclaren-mp44-ir-ayrton-senna-10330--32593893.html"/>
-    <n v="72.989999999999995"/>
+    <n v="70.989999999999995"/>
     <n v="67.989999999999995"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-23T20:05:50"/>
+    <d v="2026-05-24T14:12:06"/>
     <n v="71.89"/>
   </r>
   <r>
@@ -867,136 +1139,14 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 5"/>
-    <d v="2026-05-23T20:06:00"/>
+    <d v="2026-05-24T14:12:17"/>
     <n v="100.99"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{324A5369-8D7E-4AC2-B0C9-216B4A05F38D}" name="Vidutinė kaina" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
-  <location ref="A1:D12" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
-      <items count="11">
-        <item x="7"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField dataField="1" showAll="0" includeNewItemsInFilter="1">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField dataField="1" showAll="0" includeNewItemsInFilter="1">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField dataField="1" showAll="0" includeNewItemsInFilter="1">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField showAll="0" includeNewItemsInFilter="1">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </colItems>
-  <dataFields count="3">
-    <dataField name="Average of Pigu.lt" fld="1" subtotal="average" baseField="0" baseItem="0"/>
-    <dataField name="Average of Varle.lt" fld="2" subtotal="average" baseField="0" baseItem="0"/>
-    <dataField name="Average of Lego.com" fld="3" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24EA9CFE-ACCA-407D-AB1D-80979A8369A1}" name="Parduotuvių vertinimas" cacheId="7" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D9144D35-9AF6-4174-B024-7CDE0CE8547A}" name="Parduotuvių vertinimas" cacheId="19" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
   <location ref="A1:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
@@ -1061,7 +1211,7 @@
         </ext>
       </extLst>
     </pivotField>
-    <pivotField dataField="1" showAll="0" includeNewItemsInFilter="1">
+    <pivotField dataField="1" numFmtId="2" showAll="0" includeNewItemsInFilter="1">
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
           <x14:pivotField fillDownLabels="1"/>
@@ -1091,6 +1241,240 @@
   </colItems>
   <dataFields count="1">
     <dataField name="Sum of Galutinė kaina" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BFCF065D-4838-4845-AB0E-79FE9ED2E944}" name="Mažiausia įprasta kaina" cacheId="15" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
+  <location ref="A1:B42" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
+      <items count="11">
+        <item x="7"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="2" showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField numFmtId="2" showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField numFmtId="22" showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField numFmtId="2" showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="41">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Min of Įprasta kaina" fld="3" subtotal="min" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -1504,7 +1888,7 @@
       <c r="H1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1531,9 +1915,9 @@
         <v>23</v>
       </c>
       <c r="H2" s="2">
-        <v>46165.834456018521</v>
-      </c>
-      <c r="I2">
+        <v>46166.588263888887</v>
+      </c>
+      <c r="I2" s="3">
         <v>21.6</v>
       </c>
     </row>
@@ -1560,9 +1944,9 @@
         <v>26</v>
       </c>
       <c r="H3" s="2">
-        <v>46165.834560185183</v>
-      </c>
-      <c r="I3">
+        <v>46166.588414351849</v>
+      </c>
+      <c r="I3" s="3">
         <v>22.47</v>
       </c>
     </row>
@@ -1589,9 +1973,9 @@
         <v>28</v>
       </c>
       <c r="H4" s="2">
-        <v>46165.834722222222</v>
-      </c>
-      <c r="I4">
+        <v>46166.588553240741</v>
+      </c>
+      <c r="I4" s="3">
         <v>32.989999999999995</v>
       </c>
     </row>
@@ -1618,9 +2002,9 @@
         <v>23</v>
       </c>
       <c r="H5" s="2">
-        <v>46165.834814814814</v>
-      </c>
-      <c r="I5">
+        <v>46166.588680555556</v>
+      </c>
+      <c r="I5" s="3">
         <v>33.83</v>
       </c>
     </row>
@@ -1647,9 +2031,9 @@
         <v>31</v>
       </c>
       <c r="H6" s="2">
-        <v>46165.834918981483</v>
-      </c>
-      <c r="I6">
+        <v>46166.588819444441</v>
+      </c>
+      <c r="I6" s="3">
         <v>25.689999999999998</v>
       </c>
     </row>
@@ -1676,9 +2060,9 @@
         <v>33</v>
       </c>
       <c r="H7" s="2">
-        <v>46165.835034722222</v>
-      </c>
-      <c r="I7">
+        <v>46166.588958333334</v>
+      </c>
+      <c r="I7" s="3">
         <v>37.989999999999995</v>
       </c>
     </row>
@@ -1705,9 +2089,9 @@
         <v>23</v>
       </c>
       <c r="H8" s="2">
-        <v>46165.835138888891</v>
-      </c>
-      <c r="I8">
+        <v>46166.589085648149</v>
+      </c>
+      <c r="I8" s="3">
         <v>24.619999999999997</v>
       </c>
     </row>
@@ -1731,12 +2115,12 @@
         <v>3.9</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="H9" s="2">
-        <v>46165.835231481484</v>
-      </c>
-      <c r="I9">
+        <v>46166.589224537034</v>
+      </c>
+      <c r="I9" s="3">
         <v>18.66</v>
       </c>
     </row>
@@ -1763,9 +2147,9 @@
         <v>33</v>
       </c>
       <c r="H10" s="2">
-        <v>46165.835381944446</v>
-      </c>
-      <c r="I10">
+        <v>46166.589375000003</v>
+      </c>
+      <c r="I10" s="3">
         <v>25.99</v>
       </c>
     </row>
@@ -1792,9 +2176,9 @@
         <v>23</v>
       </c>
       <c r="H11" s="2">
-        <v>46165.835474537038</v>
-      </c>
-      <c r="I11">
+        <v>46166.589513888888</v>
+      </c>
+      <c r="I11" s="3">
         <v>159.34</v>
       </c>
     </row>
@@ -1818,12 +2202,12 @@
         <v>3.9</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H12" s="2">
-        <v>46165.835578703707</v>
-      </c>
-      <c r="I12">
+        <v>46166.58966435185</v>
+      </c>
+      <c r="I12" s="3">
         <v>159.89000000000001</v>
       </c>
     </row>
@@ -1835,7 +2219,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" s="3">
         <v>189.99</v>
@@ -1850,9 +2234,9 @@
         <v>33</v>
       </c>
       <c r="H13" s="2">
-        <v>46165.835694444446</v>
-      </c>
-      <c r="I13">
+        <v>46166.589814814812</v>
+      </c>
+      <c r="I13" s="3">
         <v>195.99</v>
       </c>
     </row>
@@ -1864,7 +2248,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" s="3">
         <v>49.95</v>
@@ -1879,9 +2263,9 @@
         <v>23</v>
       </c>
       <c r="H14" s="2">
-        <v>46165.835798611108</v>
-      </c>
-      <c r="I14">
+        <v>46166.589930555558</v>
+      </c>
+      <c r="I14" s="3">
         <v>53.440000000000005</v>
       </c>
     </row>
@@ -1893,7 +2277,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" s="3">
         <v>52.97</v>
@@ -1908,9 +2292,9 @@
         <v>31</v>
       </c>
       <c r="H15" s="2">
-        <v>46165.8358912037</v>
-      </c>
-      <c r="I15">
+        <v>46166.590069444443</v>
+      </c>
+      <c r="I15" s="3">
         <v>55.47</v>
       </c>
     </row>
@@ -1922,7 +2306,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="3">
         <v>46.99</v>
@@ -1937,9 +2321,9 @@
         <v>33</v>
       </c>
       <c r="H16" s="2">
-        <v>46165.836018518516</v>
-      </c>
-      <c r="I16">
+        <v>46166.590208333335</v>
+      </c>
+      <c r="I16" s="3">
         <v>52.99</v>
       </c>
     </row>
@@ -1951,7 +2335,7 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" s="3">
         <v>87.99</v>
@@ -1966,9 +2350,9 @@
         <v>23</v>
       </c>
       <c r="H17" s="2">
-        <v>46165.836111111108</v>
-      </c>
-      <c r="I17">
+        <v>46166.59034722222</v>
+      </c>
+      <c r="I17" s="3">
         <v>79.05</v>
       </c>
     </row>
@@ -1980,7 +2364,7 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D18" s="3">
         <v>72.989999999999995</v>
@@ -1992,12 +2376,12 @@
         <v>3.9</v>
       </c>
       <c r="G18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H18" s="2">
-        <v>46165.8362037037</v>
-      </c>
-      <c r="I18">
+        <v>46166.590486111112</v>
+      </c>
+      <c r="I18" s="3">
         <v>66.460000000000008</v>
       </c>
     </row>
@@ -2009,7 +2393,7 @@
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D19" s="3">
         <v>87.99</v>
@@ -2024,9 +2408,9 @@
         <v>33</v>
       </c>
       <c r="H19" s="2">
-        <v>46165.836331018516</v>
-      </c>
-      <c r="I19">
+        <v>46166.590624999997</v>
+      </c>
+      <c r="I19" s="3">
         <v>93.99</v>
       </c>
     </row>
@@ -2038,7 +2422,7 @@
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D20" s="3">
         <v>29.99</v>
@@ -2053,9 +2437,9 @@
         <v>23</v>
       </c>
       <c r="H20" s="2">
-        <v>46165.836423611108</v>
-      </c>
-      <c r="I20">
+        <v>46166.590763888889</v>
+      </c>
+      <c r="I20" s="3">
         <v>25.259999999999998</v>
       </c>
     </row>
@@ -2067,7 +2451,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21" s="3">
         <v>21.78</v>
@@ -2079,12 +2463,12 @@
         <v>3.9</v>
       </c>
       <c r="G21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H21" s="2">
-        <v>46165.836527777778</v>
-      </c>
-      <c r="I21">
+        <v>46166.590891203705</v>
+      </c>
+      <c r="I21" s="3">
         <v>25.68</v>
       </c>
     </row>
@@ -2096,7 +2480,7 @@
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D22" s="3">
         <v>29.99</v>
@@ -2111,9 +2495,9 @@
         <v>33</v>
       </c>
       <c r="H22" s="2">
-        <v>46165.836655092593</v>
-      </c>
-      <c r="I22">
+        <v>46166.591041666667</v>
+      </c>
+      <c r="I22" s="3">
         <v>35.989999999999995</v>
       </c>
     </row>
@@ -2125,10 +2509,10 @@
         <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D23" s="3">
-        <v>54.15</v>
+        <v>75.42</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -2140,10 +2524,10 @@
         <v>23</v>
       </c>
       <c r="H23" s="2">
-        <v>46165.836747685185</v>
-      </c>
-      <c r="I23">
-        <v>57.64</v>
+        <v>46166.591145833336</v>
+      </c>
+      <c r="I23" s="3">
+        <v>78.91</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -2154,7 +2538,7 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D24" s="3">
         <v>48.99</v>
@@ -2169,9 +2553,9 @@
         <v>31</v>
       </c>
       <c r="H24" s="2">
-        <v>46165.836863425924</v>
-      </c>
-      <c r="I24">
+        <v>46166.591226851851</v>
+      </c>
+      <c r="I24" s="3">
         <v>44.89</v>
       </c>
     </row>
@@ -2183,7 +2567,7 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D25" s="3">
         <v>59.99</v>
@@ -2198,9 +2582,9 @@
         <v>28</v>
       </c>
       <c r="H25" s="2">
-        <v>46165.836967592593</v>
-      </c>
-      <c r="I25">
+        <v>46166.591331018521</v>
+      </c>
+      <c r="I25" s="3">
         <v>65.990000000000009</v>
       </c>
     </row>
@@ -2212,7 +2596,7 @@
         <v>7</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D26" s="3">
         <v>54.99</v>
@@ -2227,9 +2611,9 @@
         <v>23</v>
       </c>
       <c r="H26" s="2">
-        <v>46165.837037037039</v>
-      </c>
-      <c r="I26">
+        <v>46166.591412037036</v>
+      </c>
+      <c r="I26" s="3">
         <v>45.39</v>
       </c>
     </row>
@@ -2241,7 +2625,7 @@
         <v>7</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D27" s="3">
         <v>42.99</v>
@@ -2256,9 +2640,9 @@
         <v>31</v>
       </c>
       <c r="H27" s="2">
-        <v>46165.837118055555</v>
-      </c>
-      <c r="I27">
+        <v>46166.591493055559</v>
+      </c>
+      <c r="I27" s="3">
         <v>45.89</v>
       </c>
     </row>
@@ -2270,7 +2654,7 @@
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D28" s="3">
         <v>54.99</v>
@@ -2285,9 +2669,9 @@
         <v>28</v>
       </c>
       <c r="H28" s="2">
-        <v>46165.837222222224</v>
-      </c>
-      <c r="I28">
+        <v>46166.591574074075</v>
+      </c>
+      <c r="I28" s="3">
         <v>49.99</v>
       </c>
     </row>
@@ -2299,7 +2683,7 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D29" s="3">
         <v>94.99</v>
@@ -2314,9 +2698,9 @@
         <v>23</v>
       </c>
       <c r="H29" s="2">
-        <v>46165.83730324074</v>
-      </c>
-      <c r="I29">
+        <v>46166.591643518521</v>
+      </c>
+      <c r="I29" s="3">
         <v>73.489999999999995</v>
       </c>
     </row>
@@ -2328,10 +2712,10 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D30" s="3">
-        <v>72.989999999999995</v>
+        <v>70.989999999999995</v>
       </c>
       <c r="E30" s="3">
         <v>67.989999999999995</v>
@@ -2343,9 +2727,9 @@
         <v>31</v>
       </c>
       <c r="H30" s="2">
-        <v>46165.837384259263</v>
-      </c>
-      <c r="I30">
+        <v>46166.591736111113</v>
+      </c>
+      <c r="I30" s="3">
         <v>71.89</v>
       </c>
     </row>
@@ -2357,7 +2741,7 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D31" s="3">
         <v>94.99</v>
@@ -2372,9 +2756,9 @@
         <v>28</v>
       </c>
       <c r="H31" s="2">
-        <v>46165.837500000001</v>
-      </c>
-      <c r="I31">
+        <v>46166.591863425929</v>
+      </c>
+      <c r="I31" s="3">
         <v>100.99</v>
       </c>
     </row>
@@ -2385,199 +2769,195 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58464371-7C24-42E3-A4DC-A9838908DB45}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E8E64FA-947F-4A37-8D6E-EEED7173DF98}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>21.6</v>
+      </c>
+      <c r="C2">
+        <v>22.47</v>
+      </c>
+      <c r="D2">
+        <v>32.989999999999995</v>
+      </c>
+      <c r="E2" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="8" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>33.83</v>
+      </c>
+      <c r="C3">
+        <v>25.69</v>
+      </c>
+      <c r="D3">
+        <v>37.989999999999995</v>
+      </c>
+      <c r="E3" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="8">
-        <v>21.6</v>
-      </c>
-      <c r="C2" s="8">
-        <v>22.47</v>
-      </c>
-      <c r="D2" s="8">
-        <v>32.989999999999995</v>
-      </c>
-      <c r="E2" s="8" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>24.62</v>
+      </c>
+      <c r="C4">
+        <v>18.66</v>
+      </c>
+      <c r="D4">
+        <v>25.99</v>
+      </c>
+      <c r="E4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="8">
-        <v>33.83</v>
-      </c>
-      <c r="C3" s="8">
-        <v>25.69</v>
-      </c>
-      <c r="D3" s="8">
-        <v>37.989999999999995</v>
-      </c>
-      <c r="E3" s="8" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>159.34</v>
+      </c>
+      <c r="C5">
+        <v>159.88999999999999</v>
+      </c>
+      <c r="D5">
+        <v>195.99</v>
+      </c>
+      <c r="E5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="8">
-        <v>24.619999999999902</v>
-      </c>
-      <c r="C4" s="8">
-        <v>18.66</v>
-      </c>
-      <c r="D4" s="8">
-        <v>25.99</v>
-      </c>
-      <c r="E4" s="8" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>53.44</v>
+      </c>
+      <c r="C6">
+        <v>55.47</v>
+      </c>
+      <c r="D6">
+        <v>52.99</v>
+      </c>
+      <c r="E6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="8">
-        <v>159.34</v>
-      </c>
-      <c r="C5" s="8">
-        <v>159.88999999999999</v>
-      </c>
-      <c r="D5" s="8">
-        <v>195.99</v>
-      </c>
-      <c r="E5" s="8" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>79.05</v>
+      </c>
+      <c r="C7">
+        <v>66.459999999999994</v>
+      </c>
+      <c r="D7">
+        <v>93.99</v>
+      </c>
+      <c r="E7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="8">
-        <v>53.44</v>
-      </c>
-      <c r="C6" s="8">
-        <v>55.47</v>
-      </c>
-      <c r="D6" s="8">
-        <v>52.99</v>
-      </c>
-      <c r="E6" s="8" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>25.26</v>
+      </c>
+      <c r="C8">
+        <v>25.68</v>
+      </c>
+      <c r="D8">
+        <v>35.989999999999995</v>
+      </c>
+      <c r="E8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>78.91</v>
+      </c>
+      <c r="C9">
+        <v>44.89</v>
+      </c>
+      <c r="D9">
+        <v>65.990000000000009</v>
+      </c>
+      <c r="E9" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="8">
-        <v>79.05</v>
-      </c>
-      <c r="C7" s="8">
-        <v>66.459999999999994</v>
-      </c>
-      <c r="D7" s="8">
-        <v>93.99</v>
-      </c>
-      <c r="E7" s="8" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>45.39</v>
+      </c>
+      <c r="C10">
+        <v>45.89</v>
+      </c>
+      <c r="D10">
+        <v>49.99</v>
+      </c>
+      <c r="E10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="8">
-        <v>25.259999999999899</v>
-      </c>
-      <c r="C8" s="8">
-        <v>25.68</v>
-      </c>
-      <c r="D8" s="8">
-        <v>35.989999999999995</v>
-      </c>
-      <c r="E8" s="8" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>73.489999999999995</v>
+      </c>
+      <c r="C11">
+        <v>71.89</v>
+      </c>
+      <c r="D11">
+        <v>100.99</v>
+      </c>
+      <c r="E11" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="8">
-        <v>57.64</v>
-      </c>
-      <c r="C9" s="8">
-        <v>44.89</v>
-      </c>
-      <c r="D9" s="8">
-        <v>65.990000000000009</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="8">
-        <v>45.39</v>
-      </c>
-      <c r="C10" s="8">
-        <v>45.89</v>
-      </c>
-      <c r="D10" s="8">
-        <v>49.99</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="8">
-        <v>73.489999999999995</v>
-      </c>
-      <c r="C11" s="8">
-        <v>71.89</v>
-      </c>
-      <c r="D11" s="8">
-        <v>100.99</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2586,191 +2966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D947CF0E-4621-439B-9599-CF319F06FACE}">
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="7">
-        <v>57.64</v>
-      </c>
-      <c r="C2" s="7">
-        <v>44.89</v>
-      </c>
-      <c r="D2" s="7">
-        <v>65.990000000000009</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="7">
-        <v>73.489999999999995</v>
-      </c>
-      <c r="C3" s="7">
-        <v>71.89</v>
-      </c>
-      <c r="D3" s="7">
-        <v>100.99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="7">
-        <v>24.619999999999902</v>
-      </c>
-      <c r="C4" s="7">
-        <v>18.66</v>
-      </c>
-      <c r="D4" s="7">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7">
-        <v>33.83</v>
-      </c>
-      <c r="C5" s="7">
-        <v>25.69</v>
-      </c>
-      <c r="D5" s="7">
-        <v>37.989999999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7">
-        <v>53.44</v>
-      </c>
-      <c r="C6" s="7">
-        <v>55.47</v>
-      </c>
-      <c r="D6" s="7">
-        <v>52.99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7">
-        <v>21.6</v>
-      </c>
-      <c r="C7" s="7">
-        <v>22.47</v>
-      </c>
-      <c r="D7" s="7">
-        <v>32.989999999999995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="7">
-        <v>79.05</v>
-      </c>
-      <c r="C8" s="7">
-        <v>66.459999999999994</v>
-      </c>
-      <c r="D8" s="7">
-        <v>93.99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="7">
-        <v>159.34</v>
-      </c>
-      <c r="C9" s="7">
-        <v>159.88999999999999</v>
-      </c>
-      <c r="D9" s="7">
-        <v>195.99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7">
-        <v>45.39</v>
-      </c>
-      <c r="C10" s="7">
-        <v>45.89</v>
-      </c>
-      <c r="D10" s="7">
-        <v>49.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="7">
-        <v>25.259999999999899</v>
-      </c>
-      <c r="C11" s="7">
-        <v>25.68</v>
-      </c>
-      <c r="D11" s="7">
-        <v>35.989999999999995</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" s="7">
-        <v>57.365999999999971</v>
-      </c>
-      <c r="C12" s="7">
-        <v>53.698999999999991</v>
-      </c>
-      <c r="D12" s="7">
-        <v>69.290000000000006</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E0866C-1D02-4161-B937-22768E10AD49}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E71E87-7911-4DEA-BA29-047073F43C4D}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2780,17 +2976,17 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="8">
         <v>692.90000000000009</v>
       </c>
     </row>
@@ -2798,24 +2994,374 @@
       <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7">
-        <v>573.66</v>
+      <c r="B3" s="8">
+        <v>594.92999999999995</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="8">
         <v>536.99</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="7">
-        <v>1803.55</v>
+        <v>72</v>
+      </c>
+      <c r="B5" s="8">
+        <v>1824.82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB7321D4-1B97-4471-AB98-B388E83AEC5C}">
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="8">
+        <v>48.99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="8">
+        <v>59.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="8">
+        <v>75.42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="8">
+        <v>48.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="8">
+        <v>70.989999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="8">
+        <v>94.99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="8">
+        <v>94.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="8">
+        <v>70.989999999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="8">
+        <v>14.76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="8">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8">
+        <v>21.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="8">
+        <v>14.76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="8">
+        <v>21.79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="8">
+        <v>31.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="8">
+        <v>31.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="8">
+        <v>21.79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="8">
+        <v>46.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="8">
+        <v>46.99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="8">
+        <v>49.95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8">
+        <v>52.97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="8">
+        <v>18.57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="8">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="8">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="8">
+        <v>18.57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="8">
+        <v>72.989999999999995</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="8">
+        <v>87.99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="8">
+        <v>87.99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="8">
+        <v>72.989999999999995</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="8">
+        <v>155.99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="8">
+        <v>189.99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="8">
+        <v>189.99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="8">
+        <v>155.99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="8">
+        <v>42.99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" s="8">
+        <v>54.99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="8">
+        <v>54.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="8">
+        <v>42.99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="8">
+        <v>21.78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="8">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="8">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" s="8">
+        <v>21.78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42" s="8">
+        <v>14.76</v>
       </c>
     </row>
   </sheetData>

--- a/Grupinis/KainuStebejimas.xlsx
+++ b/Grupinis/KainuStebejimas.xlsx
@@ -8,26 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vejas\OneDrive\Documents\UiPath\RPA\Grupinis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E83AD6-E79A-4B44-AA30-2284559FF451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F2688A-436E-42DD-A37C-88FCF13BF5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Parduotuvės" sheetId="2" r:id="rId1"/>
-    <sheet name="Prekės" sheetId="3" r:id="rId2"/>
-    <sheet name="raw_duom" sheetId="5" r:id="rId3"/>
-    <sheet name="Geriausia kaina" sheetId="12" r:id="rId4"/>
-    <sheet name="Parduotuvių vertinimas" sheetId="15" r:id="rId5"/>
-    <sheet name="Įprasta kaina" sheetId="13" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId7"/>
+    <sheet name="Prekės" sheetId="3" r:id="rId1"/>
+    <sheet name="Parduotuvės" sheetId="2" r:id="rId2"/>
+    <sheet name="raw_duom" sheetId="16" r:id="rId3"/>
+    <sheet name="Geriausia kaina" sheetId="17" r:id="rId4"/>
+    <sheet name="Įprasta kaina" sheetId="18" r:id="rId5"/>
+    <sheet name="Parduotuvių vertinimas" sheetId="19" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">raw_duom!$A$1:$I$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="15" r:id="rId8"/>
-    <pivotCache cacheId="19" r:id="rId9"/>
+    <pivotCache cacheId="24" r:id="rId7"/>
+    <pivotCache cacheId="28" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -49,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="78">
   <si>
     <t>Parduotuvė</t>
   </si>
@@ -138,15 +137,63 @@
     <t>Limit 5</t>
   </si>
   <si>
+    <t>Liko tik: 5+ vnt.</t>
+  </si>
+  <si>
+    <t>Pigu.lt</t>
+  </si>
+  <si>
+    <t>Varle.lt</t>
+  </si>
+  <si>
+    <t>Lego.com</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Galutinė kaina</t>
+  </si>
+  <si>
+    <t>Geriausia kaina</t>
+  </si>
+  <si>
+    <t>Min of Įprasta kaina</t>
+  </si>
+  <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/76443-lego-harry-potter-hagrido-ir-hario?id=125603664</t>
+  </si>
+  <si>
+    <t>https://www.varle.lt/lego/lego-harry-potter-hagrido-ir-hario-pasivazinejimas--41842791.html</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/en-lt/product/hagrid-harrys-motorcycle-ride-76443</t>
+  </si>
+  <si>
+    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-icons-mclaren-mp44-ir-ayrton-senna?id=80634865</t>
+  </si>
+  <si>
+    <t>https://www.varle.lt/lego/lego-icons-mclaren-mp44-ir-ayrton-senna-10330--32593893.html</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/en-lt/product/mclaren-mp44-ayrton-senna-10330</t>
+  </si>
+  <si>
+    <t>pigu.lt - 45.39</t>
+  </si>
+  <si>
+    <t>varle.lt - 71.89</t>
+  </si>
+  <si>
     <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-botanicals-zydintis-kaktusas-11509?id=249971577</t>
   </si>
   <si>
     <t>https://www.varle.lt/lego/lego-botanicals-zydintis-kaktusas-augalu-dekoras--50745550.html</t>
   </si>
   <si>
-    <t>Liko tik: 5+ vnt.</t>
-  </si>
-  <si>
     <t>https://www.lego.com/en-lt/product/flowering-cactus-11509</t>
   </si>
   <si>
@@ -168,6 +215,9 @@
     <t>https://www.varle.lt/lego/lego-editions-fifa-world-cuptm-oficiali-taure--50253636.html</t>
   </si>
   <si>
+    <t>Liko tik: 2 vnt.</t>
+  </si>
+  <si>
     <t>https://www.lego.com/en-lt/product/fifa-world-cup-official-trophy-43020</t>
   </si>
   <si>
@@ -186,9 +236,6 @@
     <t>https://www.varle.lt/lego/lego-art-love-31214--41770074.html</t>
   </si>
   <si>
-    <t>Liko tik: 2 vnt.</t>
-  </si>
-  <si>
     <t>https://www.lego.com/en-lt/product/love-31214</t>
   </si>
   <si>
@@ -204,39 +251,15 @@
     <t>https://www.lego.com/en-lt/product/bugatti-centodieci-hyper-sports-car-77240</t>
   </si>
   <si>
+    <t>https://pigu.lt/lt/daiktu-krepsiai/vitrina-dezute-lego-10281-bonsai-tree?id=224211668</t>
+  </si>
+  <si>
     <t>https://www.varle.lt/lego/lego-icons-bonsai-medelis-10281--15106778.html</t>
   </si>
   <si>
     <t>https://www.lego.com/en-lt/product/bonsai-tree-10281</t>
   </si>
   <si>
-    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/76443-lego-harry-potter-hagrido-ir-hario?id=125603664</t>
-  </si>
-  <si>
-    <t>https://www.varle.lt/lego/lego-harry-potter-hagrido-ir-hario-pasivazinejimas--41842791.html</t>
-  </si>
-  <si>
-    <t>https://www.lego.com/en-lt/product/hagrid-harrys-motorcycle-ride-76443</t>
-  </si>
-  <si>
-    <t>https://pigu.lt/lt/kudikiams-ir-vaikams/zaislai/konstruktoriai-ir-kaladeles/lego-icons-mclaren-mp44-ir-ayrton-senna?id=80634865</t>
-  </si>
-  <si>
-    <t>https://www.varle.lt/lego/lego-icons-mclaren-mp44-ir-ayrton-senna-10330--32593893.html</t>
-  </si>
-  <si>
-    <t>https://www.lego.com/en-lt/product/mclaren-mp44-ayrton-senna-10330</t>
-  </si>
-  <si>
-    <t>Pigu.lt</t>
-  </si>
-  <si>
-    <t>Varle.lt</t>
-  </si>
-  <si>
-    <t>Lego.com</t>
-  </si>
-  <si>
     <t>pigu.lt - 21.6</t>
   </si>
   <si>
@@ -246,7 +269,7 @@
     <t>varle.lt - 18.66</t>
   </si>
   <si>
-    <t>pigu.lt - 159.34</t>
+    <t>varle.lt - 149.18</t>
   </si>
   <si>
     <t>lego.com - 52.99</t>
@@ -255,37 +278,10 @@
     <t>varle.lt - 66.46</t>
   </si>
   <si>
+    <t>pigu.lt - 25.26</t>
+  </si>
+  <si>
     <t>varle.lt - 44.89</t>
-  </si>
-  <si>
-    <t>pigu.lt - 45.39</t>
-  </si>
-  <si>
-    <t>varle.lt - 71.89</t>
-  </si>
-  <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
-    <t>Sum of Galutinė kaina</t>
-  </si>
-  <si>
-    <t>Geriausia kaina</t>
-  </si>
-  <si>
-    <t>Liko tik: 5 vnt.</t>
-  </si>
-  <si>
-    <t>Min of Įprasta kaina</t>
-  </si>
-  <si>
-    <t>https://pigu.lt/lt/daiktu-krepsiai/vitrina-dezute-lego-10281-bonsai-tree?id=224211668</t>
-  </si>
-  <si>
-    <t>pigu.lt - 25.26</t>
   </si>
 </sst>
 </file>
@@ -373,7 +369,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46166.591880671294" createdVersion="1" refreshedVersion="8" recordCount="30" xr:uid="{2A810F29-BDBE-4F1C-8E87-98012A743E31}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46166.830656134262" createdVersion="1" refreshedVersion="8" recordCount="30" xr:uid="{9AB9364A-2C6C-4652-B34C-ACBE9525A620}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:I31" sheet="raw_duom"/>
   </cacheSource>
@@ -415,7 +411,7 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Tikrinimo laikas" numFmtId="22">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-24T14:07:06" maxDate="2026-05-24T14:12:17"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-24T19:52:14" maxDate="2026-05-24T19:56:06"/>
     </cacheField>
     <cacheField name="Galutinė kaina" numFmtId="2">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="18.66" maxValue="195.99"/>
@@ -430,7 +426,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46166.59189560185" createdVersion="1" refreshedVersion="8" recordCount="30" xr:uid="{25781A37-DFF8-4C0E-A6EA-89211E685B83}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vejas Prastienis" refreshedDate="46166.830666435184" createdVersion="1" refreshedVersion="8" recordCount="30" xr:uid="{38E8B012-51F5-4478-8B8B-1564B9D3B8E4}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:I31" sheet="raw_duom"/>
   </cacheSource>
@@ -461,7 +457,7 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Tikrinimo laikas" numFmtId="22">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-24T14:07:06" maxDate="2026-05-24T14:12:17"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-24T19:52:14" maxDate="2026-05-24T19:56:06"/>
     </cacheField>
     <cacheField name="Galutinė kaina" numFmtId="2">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="18.66" maxValue="195.99"/>
@@ -485,7 +481,7 @@
     <n v="18.11"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:07:06"/>
+    <d v="2026-05-24T19:52:14"/>
     <n v="21.6"/>
   </r>
   <r>
@@ -496,7 +492,7 @@
     <s v="Nėra"/>
     <n v="3.9"/>
     <s v="Liko tik: 4 vnt."/>
-    <d v="2026-05-24T14:07:19"/>
+    <d v="2026-05-24T19:52:23"/>
     <n v="22.47"/>
   </r>
   <r>
@@ -507,7 +503,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 5"/>
-    <d v="2026-05-24T14:07:31"/>
+    <d v="2026-05-24T19:52:33"/>
     <n v="32.989999999999995"/>
   </r>
   <r>
@@ -518,7 +514,7 @@
     <n v="30.34"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:07:42"/>
+    <d v="2026-05-24T19:52:40"/>
     <n v="33.83"/>
   </r>
   <r>
@@ -529,7 +525,7 @@
     <s v="Nėra"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-24T14:07:54"/>
+    <d v="2026-05-24T19:52:48"/>
     <n v="25.689999999999998"/>
   </r>
   <r>
@@ -540,7 +536,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-24T14:08:06"/>
+    <d v="2026-05-24T19:52:56"/>
     <n v="37.989999999999995"/>
   </r>
   <r>
@@ -551,7 +547,7 @@
     <s v="Nėra"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:08:17"/>
+    <d v="2026-05-24T19:53:04"/>
     <n v="24.619999999999997"/>
   </r>
   <r>
@@ -561,8 +557,8 @@
     <n v="14.76"/>
     <s v="Nėra"/>
     <n v="3.9"/>
-    <s v="Liko tik: 5 vnt."/>
-    <d v="2026-05-24T14:08:29"/>
+    <s v="Liko tik: 4 vnt."/>
+    <d v="2026-05-24T19:53:12"/>
     <n v="18.66"/>
   </r>
   <r>
@@ -573,7 +569,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-24T14:08:42"/>
+    <d v="2026-05-24T19:53:21"/>
     <n v="25.99"/>
   </r>
   <r>
@@ -584,19 +580,19 @@
     <n v="155.85"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:08:54"/>
+    <d v="2026-05-24T19:53:27"/>
     <n v="159.34"/>
   </r>
   <r>
     <x v="1"/>
     <x v="3"/>
     <s v="https://www.varle.lt/lego/lego-editions-fifa-world-cuptm-oficiali-taure--50253636.html"/>
-    <n v="155.99"/>
+    <n v="145.28"/>
     <s v="Nėra"/>
     <n v="3.9"/>
     <s v="Liko tik: 2 vnt."/>
-    <d v="2026-05-24T14:09:07"/>
-    <n v="159.89000000000001"/>
+    <d v="2026-05-24T19:53:35"/>
+    <n v="149.18"/>
   </r>
   <r>
     <x v="2"/>
@@ -606,7 +602,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-24T14:09:20"/>
+    <d v="2026-05-24T19:53:46"/>
     <n v="195.99"/>
   </r>
   <r>
@@ -617,7 +613,7 @@
     <s v="Nėra"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:09:30"/>
+    <d v="2026-05-24T19:53:54"/>
     <n v="53.440000000000005"/>
   </r>
   <r>
@@ -628,7 +624,7 @@
     <n v="51.57"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-24T14:09:42"/>
+    <d v="2026-05-24T19:54:01"/>
     <n v="55.47"/>
   </r>
   <r>
@@ -639,7 +635,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-24T14:09:54"/>
+    <d v="2026-05-24T19:54:10"/>
     <n v="52.99"/>
   </r>
   <r>
@@ -650,7 +646,7 @@
     <n v="75.56"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:10:06"/>
+    <d v="2026-05-24T19:54:17"/>
     <n v="79.05"/>
   </r>
   <r>
@@ -661,7 +657,7 @@
     <n v="62.56"/>
     <n v="3.9"/>
     <s v="Liko tik: 2 vnt."/>
-    <d v="2026-05-24T14:10:18"/>
+    <d v="2026-05-24T19:54:24"/>
     <n v="66.460000000000008"/>
   </r>
   <r>
@@ -672,7 +668,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-24T14:10:30"/>
+    <d v="2026-05-24T19:54:33"/>
     <n v="93.99"/>
   </r>
   <r>
@@ -683,7 +679,7 @@
     <n v="21.77"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:10:42"/>
+    <d v="2026-05-24T19:54:39"/>
     <n v="25.259999999999998"/>
   </r>
   <r>
@@ -694,7 +690,7 @@
     <s v="Nėra"/>
     <n v="3.9"/>
     <s v="Liko tik: 1 vnt."/>
-    <d v="2026-05-24T14:10:53"/>
+    <d v="2026-05-24T19:54:47"/>
     <n v="25.68"/>
   </r>
   <r>
@@ -705,7 +701,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-24T14:11:06"/>
+    <d v="2026-05-24T19:54:57"/>
     <n v="35.989999999999995"/>
   </r>
   <r>
@@ -716,7 +712,7 @@
     <s v="Nėra"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:11:15"/>
+    <d v="2026-05-24T19:55:04"/>
     <n v="78.91"/>
   </r>
   <r>
@@ -727,7 +723,7 @@
     <n v="40.99"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-24T14:11:22"/>
+    <d v="2026-05-24T19:55:11"/>
     <n v="44.89"/>
   </r>
   <r>
@@ -738,7 +734,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 5"/>
-    <d v="2026-05-24T14:11:31"/>
+    <d v="2026-05-24T19:55:22"/>
     <n v="65.990000000000009"/>
   </r>
   <r>
@@ -749,7 +745,7 @@
     <n v="41.9"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:11:38"/>
+    <d v="2026-05-24T19:55:29"/>
     <n v="45.39"/>
   </r>
   <r>
@@ -760,7 +756,7 @@
     <n v="41.99"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-24T14:11:45"/>
+    <d v="2026-05-24T19:55:36"/>
     <n v="45.89"/>
   </r>
   <r>
@@ -771,7 +767,7 @@
     <n v="43.99"/>
     <n v="6"/>
     <s v="Limit 5"/>
-    <d v="2026-05-24T14:11:52"/>
+    <d v="2026-05-24T19:55:44"/>
     <n v="49.99"/>
   </r>
   <r>
@@ -782,7 +778,7 @@
     <n v="70"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:11:58"/>
+    <d v="2026-05-24T19:55:51"/>
     <n v="73.489999999999995"/>
   </r>
   <r>
@@ -793,7 +789,7 @@
     <n v="67.989999999999995"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-24T14:12:06"/>
+    <d v="2026-05-24T19:55:57"/>
     <n v="71.89"/>
   </r>
   <r>
@@ -804,7 +800,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 5"/>
-    <d v="2026-05-24T14:12:17"/>
+    <d v="2026-05-24T19:56:06"/>
     <n v="100.99"/>
   </r>
 </pivotCacheRecords>
@@ -820,7 +816,7 @@
     <n v="18.11"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:07:06"/>
+    <d v="2026-05-24T19:52:14"/>
     <n v="21.6"/>
   </r>
   <r>
@@ -831,7 +827,7 @@
     <s v="Nėra"/>
     <n v="3.9"/>
     <s v="Liko tik: 4 vnt."/>
-    <d v="2026-05-24T14:07:19"/>
+    <d v="2026-05-24T19:52:23"/>
     <n v="22.47"/>
   </r>
   <r>
@@ -842,7 +838,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 5"/>
-    <d v="2026-05-24T14:07:31"/>
+    <d v="2026-05-24T19:52:33"/>
     <n v="32.989999999999995"/>
   </r>
   <r>
@@ -853,7 +849,7 @@
     <n v="30.34"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:07:42"/>
+    <d v="2026-05-24T19:52:40"/>
     <n v="33.83"/>
   </r>
   <r>
@@ -864,7 +860,7 @@
     <s v="Nėra"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-24T14:07:54"/>
+    <d v="2026-05-24T19:52:48"/>
     <n v="25.689999999999998"/>
   </r>
   <r>
@@ -875,7 +871,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-24T14:08:06"/>
+    <d v="2026-05-24T19:52:56"/>
     <n v="37.989999999999995"/>
   </r>
   <r>
@@ -886,7 +882,7 @@
     <s v="Nėra"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:08:17"/>
+    <d v="2026-05-24T19:53:04"/>
     <n v="24.619999999999997"/>
   </r>
   <r>
@@ -896,8 +892,8 @@
     <n v="14.76"/>
     <s v="Nėra"/>
     <n v="3.9"/>
-    <s v="Liko tik: 5 vnt."/>
-    <d v="2026-05-24T14:08:29"/>
+    <s v="Liko tik: 4 vnt."/>
+    <d v="2026-05-24T19:53:12"/>
     <n v="18.66"/>
   </r>
   <r>
@@ -908,7 +904,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-24T14:08:42"/>
+    <d v="2026-05-24T19:53:21"/>
     <n v="25.99"/>
   </r>
   <r>
@@ -919,19 +915,19 @@
     <n v="155.85"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:08:54"/>
+    <d v="2026-05-24T19:53:27"/>
     <n v="159.34"/>
   </r>
   <r>
     <x v="1"/>
     <s v="LEGO 43020"/>
     <s v="https://www.varle.lt/lego/lego-editions-fifa-world-cuptm-oficiali-taure--50253636.html"/>
-    <n v="155.99"/>
+    <n v="145.28"/>
     <s v="Nėra"/>
     <n v="3.9"/>
     <s v="Liko tik: 2 vnt."/>
-    <d v="2026-05-24T14:09:07"/>
-    <n v="159.89000000000001"/>
+    <d v="2026-05-24T19:53:35"/>
+    <n v="149.18"/>
   </r>
   <r>
     <x v="2"/>
@@ -941,7 +937,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-24T14:09:20"/>
+    <d v="2026-05-24T19:53:46"/>
     <n v="195.99"/>
   </r>
   <r>
@@ -952,7 +948,7 @@
     <s v="Nėra"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:09:30"/>
+    <d v="2026-05-24T19:53:54"/>
     <n v="53.440000000000005"/>
   </r>
   <r>
@@ -963,7 +959,7 @@
     <n v="51.57"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-24T14:09:42"/>
+    <d v="2026-05-24T19:54:01"/>
     <n v="55.47"/>
   </r>
   <r>
@@ -974,7 +970,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-24T14:09:54"/>
+    <d v="2026-05-24T19:54:10"/>
     <n v="52.99"/>
   </r>
   <r>
@@ -985,7 +981,7 @@
     <n v="75.56"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:10:06"/>
+    <d v="2026-05-24T19:54:17"/>
     <n v="79.05"/>
   </r>
   <r>
@@ -996,7 +992,7 @@
     <n v="62.56"/>
     <n v="3.9"/>
     <s v="Liko tik: 2 vnt."/>
-    <d v="2026-05-24T14:10:18"/>
+    <d v="2026-05-24T19:54:24"/>
     <n v="66.460000000000008"/>
   </r>
   <r>
@@ -1007,7 +1003,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-24T14:10:30"/>
+    <d v="2026-05-24T19:54:33"/>
     <n v="93.99"/>
   </r>
   <r>
@@ -1018,7 +1014,7 @@
     <n v="21.77"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:10:42"/>
+    <d v="2026-05-24T19:54:39"/>
     <n v="25.259999999999998"/>
   </r>
   <r>
@@ -1029,7 +1025,7 @@
     <s v="Nėra"/>
     <n v="3.9"/>
     <s v="Liko tik: 1 vnt."/>
-    <d v="2026-05-24T14:10:53"/>
+    <d v="2026-05-24T19:54:47"/>
     <n v="25.68"/>
   </r>
   <r>
@@ -1040,7 +1036,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 3"/>
-    <d v="2026-05-24T14:11:06"/>
+    <d v="2026-05-24T19:54:57"/>
     <n v="35.989999999999995"/>
   </r>
   <r>
@@ -1051,7 +1047,7 @@
     <s v="Nėra"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:11:15"/>
+    <d v="2026-05-24T19:55:04"/>
     <n v="78.91"/>
   </r>
   <r>
@@ -1062,7 +1058,7 @@
     <n v="40.99"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-24T14:11:22"/>
+    <d v="2026-05-24T19:55:11"/>
     <n v="44.89"/>
   </r>
   <r>
@@ -1073,7 +1069,7 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 5"/>
-    <d v="2026-05-24T14:11:31"/>
+    <d v="2026-05-24T19:55:22"/>
     <n v="65.990000000000009"/>
   </r>
   <r>
@@ -1084,7 +1080,7 @@
     <n v="41.9"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:11:38"/>
+    <d v="2026-05-24T19:55:29"/>
     <n v="45.39"/>
   </r>
   <r>
@@ -1095,7 +1091,7 @@
     <n v="41.99"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-24T14:11:45"/>
+    <d v="2026-05-24T19:55:36"/>
     <n v="45.89"/>
   </r>
   <r>
@@ -1106,7 +1102,7 @@
     <n v="43.99"/>
     <n v="6"/>
     <s v="Limit 5"/>
-    <d v="2026-05-24T14:11:52"/>
+    <d v="2026-05-24T19:55:44"/>
     <n v="49.99"/>
   </r>
   <r>
@@ -1117,7 +1113,7 @@
     <n v="70"/>
     <n v="3.49"/>
     <s v="Yra"/>
-    <d v="2026-05-24T14:11:58"/>
+    <d v="2026-05-24T19:55:51"/>
     <n v="73.489999999999995"/>
   </r>
   <r>
@@ -1128,7 +1124,7 @@
     <n v="67.989999999999995"/>
     <n v="3.9"/>
     <s v="Liko tik: 5+ vnt."/>
-    <d v="2026-05-24T14:12:06"/>
+    <d v="2026-05-24T19:55:57"/>
     <n v="71.89"/>
   </r>
   <r>
@@ -1139,123 +1135,14 @@
     <s v="Nėra"/>
     <n v="6"/>
     <s v="Limit 5"/>
-    <d v="2026-05-24T14:12:17"/>
+    <d v="2026-05-24T19:56:06"/>
     <n v="100.99"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D9144D35-9AF6-4174-B024-7CDE0CE8547A}" name="Parduotuvių vertinimas" cacheId="19" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
-  <location ref="A1:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
-      <items count="4">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField showAll="0" includeNewItemsInFilter="1">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField showAll="0" includeNewItemsInFilter="1">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField numFmtId="2" showAll="0" includeNewItemsInFilter="1">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField showAll="0" includeNewItemsInFilter="1">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField numFmtId="2" showAll="0" includeNewItemsInFilter="1">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField showAll="0" includeNewItemsInFilter="1">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField numFmtId="22" showAll="0" includeNewItemsInFilter="1">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="2" showAll="0" includeNewItemsInFilter="1">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Galutinė kaina" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BFCF065D-4838-4845-AB0E-79FE9ED2E944}" name="Mažiausia įprasta kaina" cacheId="15" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{29C2B418-64E4-4237-ACCD-BD79F1E03E67}" name="Mažiausia įprasta kaina" cacheId="24" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
   <location ref="A1:B42" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
@@ -1475,6 +1362,115 @@
   </colItems>
   <dataFields count="1">
     <dataField name="Min of Įprasta kaina" fld="3" subtotal="min" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FC885445-D2FF-4DC0-A8C2-F04B6CD98F0A}" name="Parduotuvių vertinimas" cacheId="28" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1">
+  <location ref="A1:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField numFmtId="2" showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField numFmtId="2" showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField numFmtId="22" showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="2" showAll="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Galutinė kaina" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -1750,6 +1746,74 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AF5DFFA-E62C-4233-BB43-6DED98E5A047}">
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{936E2D1B-75AA-4ED9-BCB5-CFD99655A6FC}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1782,85 +1846,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AF5DFFA-E62C-4233-BB43-6DED98E5A047}">
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A82665-EBC7-4EEF-96D3-7BD8C72776F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF22FBD6-FDA5-4B3A-BAEB-EA8302E94AF5}">
   <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="18.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -1888,7 +1886,7 @@
       <c r="H1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1915,7 +1913,7 @@
         <v>23</v>
       </c>
       <c r="H2" s="2">
-        <v>46166.588263888887</v>
+        <v>46166.827939814815</v>
       </c>
       <c r="I2" s="3">
         <v>21.6</v>
@@ -1944,7 +1942,7 @@
         <v>26</v>
       </c>
       <c r="H3" s="2">
-        <v>46166.588414351849</v>
+        <v>46166.828043981484</v>
       </c>
       <c r="I3" s="3">
         <v>22.47</v>
@@ -1973,7 +1971,7 @@
         <v>28</v>
       </c>
       <c r="H4" s="2">
-        <v>46166.588553240741</v>
+        <v>46166.828159722223</v>
       </c>
       <c r="I4" s="3">
         <v>32.989999999999995</v>
@@ -1987,7 +1985,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D5" s="3">
         <v>31.99</v>
@@ -2002,7 +2000,7 @@
         <v>23</v>
       </c>
       <c r="H5" s="2">
-        <v>46166.588680555556</v>
+        <v>46166.828240740739</v>
       </c>
       <c r="I5" s="3">
         <v>33.83</v>
@@ -2016,7 +2014,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D6" s="3">
         <v>21.79</v>
@@ -2028,10 +2026,10 @@
         <v>3.9</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H6" s="2">
-        <v>46166.588819444441</v>
+        <v>46166.828333333331</v>
       </c>
       <c r="I6" s="3">
         <v>25.689999999999998</v>
@@ -2045,7 +2043,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D7" s="3">
         <v>31.99</v>
@@ -2057,10 +2055,10 @@
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="H7" s="2">
-        <v>46166.588958333334</v>
+        <v>46166.828425925924</v>
       </c>
       <c r="I7" s="3">
         <v>37.989999999999995</v>
@@ -2073,8 +2071,8 @@
       <c r="B8" t="s">
         <v>2</v>
       </c>
-      <c r="C8" t="s">
-        <v>34</v>
+      <c r="C8" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="D8" s="3">
         <v>21.13</v>
@@ -2089,7 +2087,7 @@
         <v>23</v>
       </c>
       <c r="H8" s="2">
-        <v>46166.589085648149</v>
+        <v>46166.828518518516</v>
       </c>
       <c r="I8" s="3">
         <v>24.619999999999997</v>
@@ -2103,7 +2101,7 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3">
         <v>14.76</v>
@@ -2115,10 +2113,10 @@
         <v>3.9</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="H9" s="2">
-        <v>46166.589224537034</v>
+        <v>46166.828611111108</v>
       </c>
       <c r="I9" s="3">
         <v>18.66</v>
@@ -2132,7 +2130,7 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3">
         <v>19.989999999999998</v>
@@ -2144,10 +2142,10 @@
         <v>6</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="H10" s="2">
-        <v>46166.589375000003</v>
+        <v>46166.828715277778</v>
       </c>
       <c r="I10" s="3">
         <v>25.99</v>
@@ -2161,7 +2159,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D11" s="3">
         <v>189.99</v>
@@ -2176,7 +2174,7 @@
         <v>23</v>
       </c>
       <c r="H11" s="2">
-        <v>46166.589513888888</v>
+        <v>46166.828784722224</v>
       </c>
       <c r="I11" s="3">
         <v>159.34</v>
@@ -2190,10 +2188,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D12" s="3">
-        <v>155.99</v>
+        <v>145.28</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>25</v>
@@ -2202,13 +2200,13 @@
         <v>3.9</v>
       </c>
       <c r="G12" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H12" s="2">
-        <v>46166.58966435185</v>
+        <v>46166.828877314816</v>
       </c>
       <c r="I12" s="3">
-        <v>159.89000000000001</v>
+        <v>149.18</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -2219,7 +2217,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D13" s="3">
         <v>189.99</v>
@@ -2231,10 +2229,10 @@
         <v>6</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="H13" s="2">
-        <v>46166.589814814812</v>
+        <v>46166.829004629632</v>
       </c>
       <c r="I13" s="3">
         <v>195.99</v>
@@ -2248,7 +2246,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D14" s="3">
         <v>49.95</v>
@@ -2263,7 +2261,7 @@
         <v>23</v>
       </c>
       <c r="H14" s="2">
-        <v>46166.589930555558</v>
+        <v>46166.829097222224</v>
       </c>
       <c r="I14" s="3">
         <v>53.440000000000005</v>
@@ -2277,7 +2275,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D15" s="3">
         <v>52.97</v>
@@ -2289,10 +2287,10 @@
         <v>3.9</v>
       </c>
       <c r="G15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H15" s="2">
-        <v>46166.590069444443</v>
+        <v>46166.82917824074</v>
       </c>
       <c r="I15" s="3">
         <v>55.47</v>
@@ -2306,7 +2304,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D16" s="3">
         <v>46.99</v>
@@ -2318,10 +2316,10 @@
         <v>6</v>
       </c>
       <c r="G16" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="H16" s="2">
-        <v>46166.590208333335</v>
+        <v>46166.829282407409</v>
       </c>
       <c r="I16" s="3">
         <v>52.99</v>
@@ -2335,7 +2333,7 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D17" s="3">
         <v>87.99</v>
@@ -2350,7 +2348,7 @@
         <v>23</v>
       </c>
       <c r="H17" s="2">
-        <v>46166.59034722222</v>
+        <v>46166.829363425924</v>
       </c>
       <c r="I17" s="3">
         <v>79.05</v>
@@ -2364,7 +2362,7 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D18" s="3">
         <v>72.989999999999995</v>
@@ -2376,10 +2374,10 @@
         <v>3.9</v>
       </c>
       <c r="G18" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H18" s="2">
-        <v>46166.590486111112</v>
+        <v>46166.829444444447</v>
       </c>
       <c r="I18" s="3">
         <v>66.460000000000008</v>
@@ -2393,7 +2391,7 @@
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="D19" s="3">
         <v>87.99</v>
@@ -2405,10 +2403,10 @@
         <v>6</v>
       </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="H19" s="2">
-        <v>46166.590624999997</v>
+        <v>46166.829548611109</v>
       </c>
       <c r="I19" s="3">
         <v>93.99</v>
@@ -2422,7 +2420,7 @@
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="D20" s="3">
         <v>29.99</v>
@@ -2437,7 +2435,7 @@
         <v>23</v>
       </c>
       <c r="H20" s="2">
-        <v>46166.590763888889</v>
+        <v>46166.829618055555</v>
       </c>
       <c r="I20" s="3">
         <v>25.259999999999998</v>
@@ -2451,7 +2449,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D21" s="3">
         <v>21.78</v>
@@ -2463,10 +2461,10 @@
         <v>3.9</v>
       </c>
       <c r="G21" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="H21" s="2">
-        <v>46166.590891203705</v>
+        <v>46166.829710648148</v>
       </c>
       <c r="I21" s="3">
         <v>25.68</v>
@@ -2480,7 +2478,7 @@
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D22" s="3">
         <v>29.99</v>
@@ -2492,10 +2490,10 @@
         <v>6</v>
       </c>
       <c r="G22" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="H22" s="2">
-        <v>46166.591041666667</v>
+        <v>46166.829826388886</v>
       </c>
       <c r="I22" s="3">
         <v>35.989999999999995</v>
@@ -2509,7 +2507,7 @@
         <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D23" s="3">
         <v>75.42</v>
@@ -2524,7 +2522,7 @@
         <v>23</v>
       </c>
       <c r="H23" s="2">
-        <v>46166.591145833336</v>
+        <v>46166.829907407409</v>
       </c>
       <c r="I23" s="3">
         <v>78.91</v>
@@ -2538,7 +2536,7 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D24" s="3">
         <v>48.99</v>
@@ -2550,10 +2548,10 @@
         <v>3.9</v>
       </c>
       <c r="G24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H24" s="2">
-        <v>46166.591226851851</v>
+        <v>46166.829988425925</v>
       </c>
       <c r="I24" s="3">
         <v>44.89</v>
@@ -2567,7 +2565,7 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D25" s="3">
         <v>59.99</v>
@@ -2582,7 +2580,7 @@
         <v>28</v>
       </c>
       <c r="H25" s="2">
-        <v>46166.591331018521</v>
+        <v>46166.83011574074</v>
       </c>
       <c r="I25" s="3">
         <v>65.990000000000009</v>
@@ -2595,8 +2593,8 @@
       <c r="B26" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>53</v>
+      <c r="C26" t="s">
+        <v>38</v>
       </c>
       <c r="D26" s="3">
         <v>54.99</v>
@@ -2611,7 +2609,7 @@
         <v>23</v>
       </c>
       <c r="H26" s="2">
-        <v>46166.591412037036</v>
+        <v>46166.830196759256</v>
       </c>
       <c r="I26" s="3">
         <v>45.39</v>
@@ -2624,8 +2622,8 @@
       <c r="B27" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>54</v>
+      <c r="C27" t="s">
+        <v>39</v>
       </c>
       <c r="D27" s="3">
         <v>42.99</v>
@@ -2637,10 +2635,10 @@
         <v>3.9</v>
       </c>
       <c r="G27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H27" s="2">
-        <v>46166.591493055559</v>
+        <v>46166.830277777779</v>
       </c>
       <c r="I27" s="3">
         <v>45.89</v>
@@ -2654,7 +2652,7 @@
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D28" s="3">
         <v>54.99</v>
@@ -2669,7 +2667,7 @@
         <v>28</v>
       </c>
       <c r="H28" s="2">
-        <v>46166.591574074075</v>
+        <v>46166.830370370371</v>
       </c>
       <c r="I28" s="3">
         <v>49.99</v>
@@ -2683,7 +2681,7 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D29" s="3">
         <v>94.99</v>
@@ -2698,7 +2696,7 @@
         <v>23</v>
       </c>
       <c r="H29" s="2">
-        <v>46166.591643518521</v>
+        <v>46166.830451388887</v>
       </c>
       <c r="I29" s="3">
         <v>73.489999999999995</v>
@@ -2712,7 +2710,7 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D30" s="3">
         <v>70.989999999999995</v>
@@ -2724,10 +2722,10 @@
         <v>3.9</v>
       </c>
       <c r="G30" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H30" s="2">
-        <v>46166.591736111113</v>
+        <v>46166.830520833333</v>
       </c>
       <c r="I30" s="3">
         <v>71.89</v>
@@ -2741,7 +2739,7 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D31" s="3">
         <v>94.99</v>
@@ -2756,38 +2754,42 @@
         <v>28</v>
       </c>
       <c r="H31" s="2">
-        <v>46166.591863425929</v>
+        <v>46166.830625000002</v>
       </c>
       <c r="I31" s="3">
         <v>100.99</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I31" xr:uid="{B1A82665-EBC7-4EEF-96D3-7BD8C72776F6}"/>
+  <autoFilter ref="A1:I31" xr:uid="{AF22FBD6-FDA5-4B3A-BAEB-EA8302E94AF5}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E8E64FA-947F-4A37-8D6E-EEED7173DF98}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BDB4727-889D-4F19-B2BE-CC66EC97B0C8}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="E1" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2804,7 +2806,7 @@
         <v>32.989999999999995</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2821,7 +2823,7 @@
         <v>37.989999999999995</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2838,7 +2840,7 @@
         <v>25.99</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2849,13 +2851,13 @@
         <v>159.34</v>
       </c>
       <c r="C5">
-        <v>159.88999999999999</v>
+        <v>149.18</v>
       </c>
       <c r="D5">
         <v>195.99</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2872,7 +2874,7 @@
         <v>52.99</v>
       </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2889,7 +2891,7 @@
         <v>93.99</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2906,7 +2908,7 @@
         <v>35.989999999999995</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -2923,7 +2925,7 @@
         <v>65.990000000000009</v>
       </c>
       <c r="E9" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -2940,7 +2942,7 @@
         <v>49.99</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -2957,7 +2959,7 @@
         <v>100.99</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2966,7 +2968,357 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E71E87-7911-4DEA-BA29-047073F43C4D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39AFEC5B-4A2A-41B5-A1F9-0E01286F69C7}">
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="8">
+        <v>48.99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="8">
+        <v>59.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="8">
+        <v>75.42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="8">
+        <v>48.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="8">
+        <v>70.989999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="8">
+        <v>94.99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="8">
+        <v>94.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="8">
+        <v>70.989999999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="8">
+        <v>14.76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="8">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8">
+        <v>21.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="8">
+        <v>14.76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="8">
+        <v>21.79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="8">
+        <v>31.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="8">
+        <v>31.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="8">
+        <v>21.79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="8">
+        <v>46.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="8">
+        <v>46.99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="8">
+        <v>49.95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8">
+        <v>52.97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="8">
+        <v>18.57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="8">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="8">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="8">
+        <v>18.57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="8">
+        <v>72.989999999999995</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="8">
+        <v>87.99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="8">
+        <v>87.99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="8">
+        <v>72.989999999999995</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="8">
+        <v>145.28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="8">
+        <v>189.99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="8">
+        <v>189.99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="8">
+        <v>145.28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="8">
+        <v>42.99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" s="8">
+        <v>54.99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="8">
+        <v>54.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="8">
+        <v>42.99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="8">
+        <v>21.78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="8">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="8">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" s="8">
+        <v>21.78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B42" s="8">
+        <v>14.76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAC43234-FE76-456C-B250-F9D1412AAA97}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2976,10 +3328,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -3003,425 +3355,15 @@
         <v>20</v>
       </c>
       <c r="B4" s="8">
-        <v>536.99</v>
+        <v>526.28000000000009</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="B5" s="8">
-        <v>1824.82</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB7321D4-1B97-4471-AB98-B388E83AEC5C}">
-  <dimension ref="A1:B42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="8">
-        <v>48.99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="8">
-        <v>59.99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="8">
-        <v>75.42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="8">
-        <v>48.99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="8">
-        <v>70.989999999999995</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="8">
-        <v>94.99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="8">
-        <v>94.99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="8">
-        <v>70.989999999999995</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="8">
-        <v>14.76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="8">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="8">
-        <v>21.13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="8">
-        <v>14.76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="8">
-        <v>21.79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="8">
-        <v>31.99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="8">
-        <v>31.99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="8">
-        <v>21.79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="8">
-        <v>46.99</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="8">
-        <v>46.99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="8">
-        <v>49.95</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="8">
-        <v>52.97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="8">
-        <v>18.57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="8">
-        <v>26.99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="8">
-        <v>26.99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="8">
-        <v>18.57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="8">
-        <v>72.989999999999995</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="8">
-        <v>87.99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="8">
-        <v>87.99</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" s="8">
-        <v>72.989999999999995</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="8">
-        <v>155.99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B31" s="8">
-        <v>189.99</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" s="8">
-        <v>189.99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33" s="8">
-        <v>155.99</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="8">
-        <v>42.99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B35" s="8">
-        <v>54.99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" s="8">
-        <v>54.99</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B37" s="8">
-        <v>42.99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38" s="8">
-        <v>21.78</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" s="8">
-        <v>29.99</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B40" s="8">
-        <v>29.99</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B41" s="8">
-        <v>21.78</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B42" s="8">
-        <v>14.76</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D797EC2-8ECA-4DB3-8F97-C4723F363B42}">
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>8</v>
+        <v>1814.1100000000001</v>
       </c>
     </row>
   </sheetData>
